--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -55,112 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
-  <si>
-    <t>ArrowMakeupGuideUIForm.go</t>
-  </si>
-  <si>
-    <t>行こう</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip1</t>
-  </si>
-  <si>
-    <t>ゲームを聴いて、報酬を得る</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip2</t>
-  </si>
-  <si>
-    <t>お金を稼ぐ準備ができている！</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.Title</t>
-  </si>
-  <si>
-    <t>ゲームガイド</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.account</t>
-  </si>
-  <si>
-    <t>アカウント</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.continue</t>
-  </si>
-  <si>
-    <t>続ける</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.payment</t>
-  </si>
-  <si>
-    <t>支払いルート</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.rebind</t>
-  </si>
-  <si>
-    <t>再バインド</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.tips</t>
-  </si>
-  <si>
-    <t>ヒント</t>
-  </si>
-  <si>
-    <t>ArrowMakeupOrdemUIForm.record</t>
-  </si>
-  <si>
-    <t>事件の記録を取り下げる</t>
-  </si>
-  <si>
-    <t>ArrowMakeupTipsUIForm.Text_Title</t>
-  </si>
-  <si>
-    <t>指示を撤回する.</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.makeup</t>
-  </si>
-  <si>
-    <t>抽出</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.play</t>
-  </si>
-  <si>
-    <t>遊びに行く</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.title</t>
-  </si>
-  <si>
-    <t>引き出し要求</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.curBankInfo</t>
-  </si>
-  <si>
-    <t>支払い方法を選択してください。</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">引き出し比率： </t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.tile</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.title_text</t>
-  </si>
-  <si>
-    <t>つりあい</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -186,22 +81,10 @@
     <t>消去する矢印を選択してください</t>
   </si>
   <si>
-    <t>ArrowMazeUIForm.ItemAutoRemoveFail</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>ArrowMazeUIForm.LevelTxt</t>
   </si>
   <si>
     <t>レベル＃0＃</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.makeuptxt</t>
-  </si>
-  <si>
-    <t>抽出するために収集＃0＃！</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -217,6 +100,9 @@
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.Continue</t>
+  </si>
+  <si>
+    <t>続ける</t>
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.NextLevel</t>
@@ -238,45 +124,6 @@
   </si>
   <si>
     <t>ArrowRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.claim</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.Notchanks</t>
-  </si>
-  <si>
-    <t>いいえ、結構です。</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardUIForm.check</t>
-  </si>
-  <si>
-    <t>小切手カード</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.Confirm</t>
-  </si>
-  <si>
-    <t>確認</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>あなたの＃0＃勘定科目を入力してください</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title</t>
-  </si>
-  <si>
-    <t>引き出し方式</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title_1</t>
-  </si>
-  <si>
-    <t>プラットフォーム</t>
   </si>
   <si>
     <t>ArrowSettingController.OFF</t>
@@ -461,6 +308,12 @@
   <si>
     <t>再収集＃0＃</t>
   </si>
+  <si>
+    <t>TaskItem.infoTxt</t>
+  </si>
+  <si>
+    <t/>
+  </si>
 </sst>
 </file>
 
@@ -571,27 +424,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -599,43 +452,43 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -643,42 +496,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -686,96 +519,12 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -788,6 +537,286 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -7140,2252 +7169,16 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1139">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1140">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1141">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1142">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1143">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1144">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1145">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1146">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1147">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1148">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1149">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1150">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1151">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1152">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1153">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1154">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1155">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1155"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>62</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1156">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1156"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>63</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1157">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1157"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1158">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1158"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1159">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1159"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A66" id="1160">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1160"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>67</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A67" id="1161">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1161"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>67</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A68" id="1162">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1162"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1163">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1163"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1164">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1164"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.737557547433" customWidth="1"/>
+    <col min="2" max="2" width="34.0738721575056" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9494,151 +7287,151 @@
         <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="0" t="s">
         <v>24</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="0" t="s">
         <v>28</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="0" t="s">
         <v>30</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="0" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="0" t="s">
         <v>45</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="0" t="s">
         <v>47</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="0" t="s">
         <v>49</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="0" t="s">
         <v>51</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="0" t="s">
         <v>53</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -9674,349 +7467,115 @@
         <v>60</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="0" t="s">
         <v>85</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1"/>
-      <c r="B47" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1"/>
-      <c r="B48" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1"/>
-      <c r="B49" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1"/>
-      <c r="B50" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1"/>
-      <c r="B51" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1"/>
-      <c r="B52" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1"/>
-      <c r="B53" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1"/>
-      <c r="B54" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1"/>
-      <c r="B55" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1"/>
-      <c r="B56" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1"/>
-      <c r="B57" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1"/>
-      <c r="B58" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1"/>
-      <c r="B59" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1"/>
-      <c r="B60" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1"/>
-      <c r="B61" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1"/>
-      <c r="B62" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1"/>
-      <c r="B63" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1"/>
-      <c r="B65" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1"/>
-      <c r="B66" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1"/>
-      <c r="B67" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1"/>
-      <c r="B68" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1"/>
-      <c r="B69" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="C69" s="0" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1"/>
-      <c r="B70" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -10028,7 +7587,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId637" name="A1">
+            <control shapeId="1095" r:id="rId706" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10050,7 +7609,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId638" name="A2">
+            <control shapeId="1096" r:id="rId707" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10072,7 +7631,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId639" name="A3">
+            <control shapeId="1097" r:id="rId708" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10094,7 +7653,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId640" name="A4">
+            <control shapeId="1098" r:id="rId709" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10116,7 +7675,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId641" name="A5">
+            <control shapeId="1099" r:id="rId710" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10138,7 +7697,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId642" name="A6">
+            <control shapeId="1100" r:id="rId711" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10160,7 +7719,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId643" name="A7">
+            <control shapeId="1101" r:id="rId712" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10182,7 +7741,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId644" name="A8">
+            <control shapeId="1102" r:id="rId713" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10204,7 +7763,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId645" name="A9">
+            <control shapeId="1103" r:id="rId714" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10226,7 +7785,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId646" name="A10">
+            <control shapeId="1104" r:id="rId715" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10248,7 +7807,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId647" name="A11">
+            <control shapeId="1105" r:id="rId716" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10270,7 +7829,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId648" name="A12">
+            <control shapeId="1106" r:id="rId717" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10292,7 +7851,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId649" name="A13">
+            <control shapeId="1107" r:id="rId718" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10314,7 +7873,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId650" name="A14">
+            <control shapeId="1108" r:id="rId719" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10336,7 +7895,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId651" name="A15">
+            <control shapeId="1109" r:id="rId720" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10358,7 +7917,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId652" name="A16">
+            <control shapeId="1110" r:id="rId721" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10380,7 +7939,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId653" name="A17">
+            <control shapeId="1111" r:id="rId722" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10402,7 +7961,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId654" name="A18">
+            <control shapeId="1112" r:id="rId723" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10424,7 +7983,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId655" name="A19">
+            <control shapeId="1113" r:id="rId724" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10446,7 +8005,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId656" name="A20">
+            <control shapeId="1114" r:id="rId725" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10468,7 +8027,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId657" name="A21">
+            <control shapeId="1115" r:id="rId726" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10490,7 +8049,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId658" name="A22">
+            <control shapeId="1116" r:id="rId727" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10512,7 +8071,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId659" name="A23">
+            <control shapeId="1117" r:id="rId728" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10534,7 +8093,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId660" name="A24">
+            <control shapeId="1118" r:id="rId729" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10556,7 +8115,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId661" name="A25">
+            <control shapeId="1119" r:id="rId730" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10578,7 +8137,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId662" name="A26">
+            <control shapeId="1120" r:id="rId731" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10600,7 +8159,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId663" name="A27">
+            <control shapeId="1121" r:id="rId732" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10622,7 +8181,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId664" name="A28">
+            <control shapeId="1122" r:id="rId733" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10644,7 +8203,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId665" name="A29">
+            <control shapeId="1123" r:id="rId734" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10666,7 +8225,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId666" name="A30">
+            <control shapeId="1124" r:id="rId735" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10688,7 +8247,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId667" name="A31">
+            <control shapeId="1125" r:id="rId736" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10710,7 +8269,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId668" name="A32">
+            <control shapeId="1126" r:id="rId737" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10732,7 +8291,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId669" name="A33">
+            <control shapeId="1127" r:id="rId738" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10754,7 +8313,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId670" name="A34">
+            <control shapeId="1128" r:id="rId739" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10776,7 +8335,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId671" name="A35">
+            <control shapeId="1129" r:id="rId740" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10798,7 +8357,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId672" name="A36">
+            <control shapeId="1130" r:id="rId741" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10820,7 +8379,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId673" name="A37">
+            <control shapeId="1131" r:id="rId742" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10842,7 +8401,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId674" name="A38">
+            <control shapeId="1132" r:id="rId743" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10864,7 +8423,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId675" name="A39">
+            <control shapeId="1133" r:id="rId744" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10886,7 +8445,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId676" name="A40">
+            <control shapeId="1134" r:id="rId745" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10908,7 +8467,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId677" name="A41">
+            <control shapeId="1135" r:id="rId746" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10930,7 +8489,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId678" name="A42">
+            <control shapeId="1136" r:id="rId747" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10952,7 +8511,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId679" name="A43">
+            <control shapeId="1137" r:id="rId748" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10974,7 +8533,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId680" name="A44">
+            <control shapeId="1138" r:id="rId749" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10987,578 +8546,6 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>44</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId681" name="A45">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>44</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId682" name="A46">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId683" name="A47">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId684" name="A48">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>48</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId685" name="A49">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>48</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>49</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId686" name="A50">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>49</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>50</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId687" name="A51">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>50</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>51</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId688" name="A52">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>51</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>52</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId689" name="A53">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>52</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>53</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId690" name="A54">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>53</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>54</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId691" name="A55">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>54</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>55</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId692" name="A56">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>55</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>56</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId693" name="A57">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>56</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>57</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId694" name="A58">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>57</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>58</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId695" name="A59">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>58</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>59</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId696" name="A60">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>59</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>60</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1155" r:id="rId697" name="A61">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>60</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>61</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1156" r:id="rId698" name="A62">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>61</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>62</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1157" r:id="rId699" name="A63">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>62</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>63</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1158" r:id="rId700" name="A64">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>63</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1159" r:id="rId701" name="A65">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1160" r:id="rId702" name="A66">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1161" r:id="rId703" name="A67">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>67</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1162" r:id="rId704" name="A68">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>67</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1163" r:id="rId705" name="A69">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1164" r:id="rId706" name="A70">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>70</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -309,10 +309,13 @@
     <t>再収集＃0＃</t>
   </si>
   <si>
-    <t>TaskItem.infoTxt</t>
+    <t>MakeupUIForm.title</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>TaskItem.infoTxt</t>
   </si>
 </sst>
 </file>
@@ -515,6 +518,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -3386,6 +3393,182 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3402,10 +3585,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1095">
+            <xdr:cNvPr hidden="1" name="A1" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3488,10 +3671,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1096">
+            <xdr:cNvPr hidden="1" name="A2" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3574,10 +3757,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1097">
+            <xdr:cNvPr hidden="1" name="A3" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3660,10 +3843,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1098">
+            <xdr:cNvPr hidden="1" name="A4" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3746,10 +3929,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1099">
+            <xdr:cNvPr hidden="1" name="A5" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3832,10 +4015,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1100">
+            <xdr:cNvPr hidden="1" name="A6" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3918,10 +4101,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1101">
+            <xdr:cNvPr hidden="1" name="A7" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4004,10 +4187,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1102">
+            <xdr:cNvPr hidden="1" name="A8" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4090,10 +4273,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1103">
+            <xdr:cNvPr hidden="1" name="A9" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4176,10 +4359,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1104">
+            <xdr:cNvPr hidden="1" name="A10" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4262,10 +4445,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1105">
+            <xdr:cNvPr hidden="1" name="A11" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4348,10 +4531,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1106">
+            <xdr:cNvPr hidden="1" name="A12" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4434,10 +4617,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1107">
+            <xdr:cNvPr hidden="1" name="A13" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4520,10 +4703,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1108">
+            <xdr:cNvPr hidden="1" name="A14" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4606,10 +4789,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1109">
+            <xdr:cNvPr hidden="1" name="A15" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4692,10 +4875,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1110">
+            <xdr:cNvPr hidden="1" name="A16" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4778,10 +4961,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1111">
+            <xdr:cNvPr hidden="1" name="A17" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1111"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4864,10 +5047,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1112">
+            <xdr:cNvPr hidden="1" name="A18" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1112"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4950,10 +5133,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1113">
+            <xdr:cNvPr hidden="1" name="A19" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5036,10 +5219,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1114">
+            <xdr:cNvPr hidden="1" name="A20" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5122,10 +5305,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1115">
+            <xdr:cNvPr hidden="1" name="A21" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5208,10 +5391,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1116">
+            <xdr:cNvPr hidden="1" name="A22" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5294,10 +5477,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1117">
+            <xdr:cNvPr hidden="1" name="A23" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5380,10 +5563,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1118">
+            <xdr:cNvPr hidden="1" name="A24" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5466,10 +5649,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1119">
+            <xdr:cNvPr hidden="1" name="A25" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5552,10 +5735,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1120">
+            <xdr:cNvPr hidden="1" name="A26" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5638,10 +5821,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1121">
+            <xdr:cNvPr hidden="1" name="A27" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
+                  <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5724,10 +5907,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1122">
+            <xdr:cNvPr hidden="1" name="A28" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1122"/>
+                  <a14:compatExt spid="_x0000_s1096"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5810,10 +5993,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1123">
+            <xdr:cNvPr hidden="1" name="A29" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1123"/>
+                  <a14:compatExt spid="_x0000_s1097"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5896,10 +6079,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1124">
+            <xdr:cNvPr hidden="1" name="A30" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1124"/>
+                  <a14:compatExt spid="_x0000_s1098"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5982,10 +6165,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1125">
+            <xdr:cNvPr hidden="1" name="A31" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1125"/>
+                  <a14:compatExt spid="_x0000_s1099"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6068,10 +6251,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1126">
+            <xdr:cNvPr hidden="1" name="A32" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1126"/>
+                  <a14:compatExt spid="_x0000_s1100"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6154,10 +6337,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1127">
+            <xdr:cNvPr hidden="1" name="A33" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1127"/>
+                  <a14:compatExt spid="_x0000_s1101"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6240,10 +6423,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1128">
+            <xdr:cNvPr hidden="1" name="A34" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1128"/>
+                  <a14:compatExt spid="_x0000_s1102"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6326,10 +6509,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1129">
+            <xdr:cNvPr hidden="1" name="A35" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1129"/>
+                  <a14:compatExt spid="_x0000_s1103"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6412,10 +6595,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1130">
+            <xdr:cNvPr hidden="1" name="A36" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1130"/>
+                  <a14:compatExt spid="_x0000_s1104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6498,10 +6681,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1131">
+            <xdr:cNvPr hidden="1" name="A37" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1131"/>
+                  <a14:compatExt spid="_x0000_s1105"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6584,10 +6767,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1132">
+            <xdr:cNvPr hidden="1" name="A38" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1132"/>
+                  <a14:compatExt spid="_x0000_s1106"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6670,10 +6853,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1133">
+            <xdr:cNvPr hidden="1" name="A39" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1133"/>
+                  <a14:compatExt spid="_x0000_s1107"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6756,10 +6939,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1134">
+            <xdr:cNvPr hidden="1" name="A40" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1134"/>
+                  <a14:compatExt spid="_x0000_s1108"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6842,10 +7025,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1135">
+            <xdr:cNvPr hidden="1" name="A41" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1135"/>
+                  <a14:compatExt spid="_x0000_s1109"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6928,10 +7111,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1136">
+            <xdr:cNvPr hidden="1" name="A42" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1136"/>
+                  <a14:compatExt spid="_x0000_s1110"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7014,10 +7197,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1137">
+            <xdr:cNvPr hidden="1" name="A43" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
+                  <a14:compatExt spid="_x0000_s1111"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7100,10 +7283,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1138">
+            <xdr:cNvPr hidden="1" name="A44" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
+                  <a14:compatExt spid="_x0000_s1112"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7169,12 +7352,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A45" id="1113">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1113"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -7578,6 +7847,15 @@
         <v>85</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -7587,7 +7865,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId706" name="A1">
+            <control shapeId="1069" r:id="rId749" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7609,7 +7887,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId707" name="A2">
+            <control shapeId="1070" r:id="rId750" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7631,7 +7909,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId708" name="A3">
+            <control shapeId="1071" r:id="rId751" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7653,7 +7931,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId709" name="A4">
+            <control shapeId="1072" r:id="rId752" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7675,7 +7953,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId710" name="A5">
+            <control shapeId="1073" r:id="rId753" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7697,7 +7975,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId711" name="A6">
+            <control shapeId="1074" r:id="rId754" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7719,7 +7997,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId712" name="A7">
+            <control shapeId="1075" r:id="rId755" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7741,7 +8019,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId713" name="A8">
+            <control shapeId="1076" r:id="rId756" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7763,7 +8041,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId714" name="A9">
+            <control shapeId="1077" r:id="rId757" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7785,7 +8063,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId715" name="A10">
+            <control shapeId="1078" r:id="rId758" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7807,7 +8085,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId716" name="A11">
+            <control shapeId="1079" r:id="rId759" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7829,7 +8107,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId717" name="A12">
+            <control shapeId="1080" r:id="rId760" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7851,7 +8129,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId718" name="A13">
+            <control shapeId="1081" r:id="rId761" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7873,7 +8151,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId719" name="A14">
+            <control shapeId="1082" r:id="rId762" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7895,7 +8173,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId720" name="A15">
+            <control shapeId="1083" r:id="rId763" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7917,7 +8195,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId721" name="A16">
+            <control shapeId="1084" r:id="rId764" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7939,7 +8217,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId722" name="A17">
+            <control shapeId="1085" r:id="rId765" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7961,7 +8239,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId723" name="A18">
+            <control shapeId="1086" r:id="rId766" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7983,7 +8261,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId724" name="A19">
+            <control shapeId="1087" r:id="rId767" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8005,7 +8283,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId725" name="A20">
+            <control shapeId="1088" r:id="rId768" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8027,7 +8305,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId726" name="A21">
+            <control shapeId="1089" r:id="rId769" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8049,7 +8327,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId727" name="A22">
+            <control shapeId="1090" r:id="rId770" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8071,7 +8349,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId728" name="A23">
+            <control shapeId="1091" r:id="rId771" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8093,7 +8371,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId729" name="A24">
+            <control shapeId="1092" r:id="rId772" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8115,7 +8393,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId730" name="A25">
+            <control shapeId="1093" r:id="rId773" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8137,7 +8415,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId731" name="A26">
+            <control shapeId="1094" r:id="rId774" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8159,7 +8437,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId732" name="A27">
+            <control shapeId="1095" r:id="rId775" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8181,7 +8459,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId733" name="A28">
+            <control shapeId="1096" r:id="rId776" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8203,7 +8481,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId734" name="A29">
+            <control shapeId="1097" r:id="rId777" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8225,7 +8503,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId735" name="A30">
+            <control shapeId="1098" r:id="rId778" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8247,7 +8525,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId736" name="A31">
+            <control shapeId="1099" r:id="rId779" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8269,7 +8547,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId737" name="A32">
+            <control shapeId="1100" r:id="rId780" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8291,7 +8569,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId738" name="A33">
+            <control shapeId="1101" r:id="rId781" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8313,7 +8591,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId739" name="A34">
+            <control shapeId="1102" r:id="rId782" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8335,7 +8613,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId740" name="A35">
+            <control shapeId="1103" r:id="rId783" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8357,7 +8635,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId741" name="A36">
+            <control shapeId="1104" r:id="rId784" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8379,7 +8657,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId742" name="A37">
+            <control shapeId="1105" r:id="rId785" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8401,7 +8679,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId743" name="A38">
+            <control shapeId="1106" r:id="rId786" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8423,7 +8701,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId744" name="A39">
+            <control shapeId="1107" r:id="rId787" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8445,7 +8723,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId745" name="A40">
+            <control shapeId="1108" r:id="rId788" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8467,7 +8745,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId746" name="A41">
+            <control shapeId="1109" r:id="rId789" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8489,7 +8767,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId747" name="A42">
+            <control shapeId="1110" r:id="rId790" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8511,7 +8789,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId748" name="A43">
+            <control shapeId="1111" r:id="rId791" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8533,7 +8811,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId749" name="A44">
+            <control shapeId="1112" r:id="rId792" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8546,6 +8824,28 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>44</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1113" r:id="rId793" name="A45">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>44</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>45</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -297,6 +297,15 @@
     <t>交換に失敗して残念です。</t>
   </si>
   <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
@@ -310,9 +319,6 @@
   </si>
   <si>
     <t>MakeupUIForm.title</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -515,10 +521,18 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -3569,6 +3583,370 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3585,179 +3963,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1069">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1070">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1071">
+            <xdr:cNvPr hidden="1" name="A1" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -3832,18 +4038,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1072">
+            <xdr:cNvPr hidden="1" name="A2" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -3918,18 +4124,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1073">
+            <xdr:cNvPr hidden="1" name="A3" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -4004,18 +4210,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1074">
+            <xdr:cNvPr hidden="1" name="A4" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -4090,18 +4296,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1075">
+            <xdr:cNvPr hidden="1" name="A5" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -4176,18 +4382,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1076">
+            <xdr:cNvPr hidden="1" name="A6" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -4262,18 +4468,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1077">
+            <xdr:cNvPr hidden="1" name="A7" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -4348,18 +4554,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1078">
+            <xdr:cNvPr hidden="1" name="A8" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -4434,18 +4640,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1079">
+            <xdr:cNvPr hidden="1" name="A9" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -4520,18 +4726,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1080">
+            <xdr:cNvPr hidden="1" name="A10" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -4606,18 +4812,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1081">
+            <xdr:cNvPr hidden="1" name="A11" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -4692,18 +4898,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1082">
+            <xdr:cNvPr hidden="1" name="A12" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -4778,18 +4984,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1083">
+            <xdr:cNvPr hidden="1" name="A13" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -4864,18 +5070,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1084">
+            <xdr:cNvPr hidden="1" name="A14" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -4950,18 +5156,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1085">
+            <xdr:cNvPr hidden="1" name="A15" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -5036,18 +5242,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1086">
+            <xdr:cNvPr hidden="1" name="A16" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -5122,18 +5328,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1087">
+            <xdr:cNvPr hidden="1" name="A17" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -5208,18 +5414,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1088">
+            <xdr:cNvPr hidden="1" name="A18" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -5294,18 +5500,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1089">
+            <xdr:cNvPr hidden="1" name="A19" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -5380,18 +5586,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1090">
+            <xdr:cNvPr hidden="1" name="A20" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -5466,18 +5672,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1091">
+            <xdr:cNvPr hidden="1" name="A21" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -5552,18 +5758,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1092">
+            <xdr:cNvPr hidden="1" name="A22" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -5638,18 +5844,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1093">
+            <xdr:cNvPr hidden="1" name="A23" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -5724,18 +5930,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1094">
+            <xdr:cNvPr hidden="1" name="A24" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -5810,18 +6016,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1095">
+            <xdr:cNvPr hidden="1" name="A25" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -5896,18 +6102,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1096">
+            <xdr:cNvPr hidden="1" name="A26" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -5982,18 +6188,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1097">
+            <xdr:cNvPr hidden="1" name="A27" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -6068,18 +6274,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1098">
+            <xdr:cNvPr hidden="1" name="A28" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -6154,18 +6360,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1099">
+            <xdr:cNvPr hidden="1" name="A29" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -6240,18 +6446,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1100">
+            <xdr:cNvPr hidden="1" name="A30" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -6326,18 +6532,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1101">
+            <xdr:cNvPr hidden="1" name="A31" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -6412,18 +6618,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1102">
+            <xdr:cNvPr hidden="1" name="A32" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -6498,18 +6704,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1103">
+            <xdr:cNvPr hidden="1" name="A33" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -6584,18 +6790,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1104">
+            <xdr:cNvPr hidden="1" name="A34" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -6670,18 +6876,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1105">
+            <xdr:cNvPr hidden="1" name="A35" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -6756,18 +6962,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1106">
+            <xdr:cNvPr hidden="1" name="A36" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -6842,18 +7048,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1107">
+            <xdr:cNvPr hidden="1" name="A37" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -6928,18 +7134,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1108">
+            <xdr:cNvPr hidden="1" name="A38" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -7014,18 +7220,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1109">
+            <xdr:cNvPr hidden="1" name="A39" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -7100,18 +7306,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1110">
+            <xdr:cNvPr hidden="1" name="A40" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -7186,18 +7392,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1111">
+            <xdr:cNvPr hidden="1" name="A41" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -7272,18 +7478,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1112">
+            <xdr:cNvPr hidden="1" name="A42" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -7358,18 +7564,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1113">
+            <xdr:cNvPr hidden="1" name="A43" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -7438,12 +7644,356 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A44" id="1114">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1114"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A45" id="1115">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1115"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A46" id="1116">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1116"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1117">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1117"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -7835,25 +8385,43 @@
         <v>82</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>85</v>
+    </row>
+    <row r="46">
+      <c r="A46" s="1"/>
+      <c r="B46" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1"/>
+      <c r="B47" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -7865,7 +8433,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId749" name="A1">
+            <control shapeId="1071" r:id="rId838" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7887,7 +8455,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId750" name="A2">
+            <control shapeId="1072" r:id="rId839" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7909,7 +8477,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId751" name="A3">
+            <control shapeId="1073" r:id="rId840" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7931,7 +8499,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId752" name="A4">
+            <control shapeId="1074" r:id="rId841" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7953,7 +8521,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId753" name="A5">
+            <control shapeId="1075" r:id="rId842" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7975,7 +8543,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId754" name="A6">
+            <control shapeId="1076" r:id="rId843" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7997,7 +8565,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId755" name="A7">
+            <control shapeId="1077" r:id="rId844" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8019,7 +8587,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId756" name="A8">
+            <control shapeId="1078" r:id="rId845" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8041,7 +8609,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId757" name="A9">
+            <control shapeId="1079" r:id="rId846" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8063,7 +8631,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId758" name="A10">
+            <control shapeId="1080" r:id="rId847" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8085,7 +8653,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId759" name="A11">
+            <control shapeId="1081" r:id="rId848" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8107,7 +8675,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId760" name="A12">
+            <control shapeId="1082" r:id="rId849" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8129,7 +8697,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId761" name="A13">
+            <control shapeId="1083" r:id="rId850" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8151,7 +8719,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId762" name="A14">
+            <control shapeId="1084" r:id="rId851" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8173,7 +8741,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId763" name="A15">
+            <control shapeId="1085" r:id="rId852" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8195,7 +8763,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId764" name="A16">
+            <control shapeId="1086" r:id="rId853" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8217,7 +8785,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId765" name="A17">
+            <control shapeId="1087" r:id="rId854" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8239,7 +8807,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId766" name="A18">
+            <control shapeId="1088" r:id="rId855" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8261,7 +8829,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId767" name="A19">
+            <control shapeId="1089" r:id="rId856" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8283,7 +8851,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId768" name="A20">
+            <control shapeId="1090" r:id="rId857" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8305,7 +8873,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId769" name="A21">
+            <control shapeId="1091" r:id="rId858" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8327,7 +8895,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId770" name="A22">
+            <control shapeId="1092" r:id="rId859" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8349,7 +8917,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId771" name="A23">
+            <control shapeId="1093" r:id="rId860" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8371,7 +8939,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId772" name="A24">
+            <control shapeId="1094" r:id="rId861" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8393,7 +8961,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId773" name="A25">
+            <control shapeId="1095" r:id="rId862" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8415,7 +8983,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId774" name="A26">
+            <control shapeId="1096" r:id="rId863" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8437,7 +9005,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId775" name="A27">
+            <control shapeId="1097" r:id="rId864" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8459,7 +9027,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId776" name="A28">
+            <control shapeId="1098" r:id="rId865" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8481,7 +9049,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId777" name="A29">
+            <control shapeId="1099" r:id="rId866" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8503,7 +9071,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId778" name="A30">
+            <control shapeId="1100" r:id="rId867" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8525,7 +9093,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId779" name="A31">
+            <control shapeId="1101" r:id="rId868" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8547,7 +9115,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId780" name="A32">
+            <control shapeId="1102" r:id="rId869" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8569,7 +9137,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId781" name="A33">
+            <control shapeId="1103" r:id="rId870" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8591,7 +9159,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId782" name="A34">
+            <control shapeId="1104" r:id="rId871" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8613,7 +9181,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId783" name="A35">
+            <control shapeId="1105" r:id="rId872" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8635,7 +9203,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId784" name="A36">
+            <control shapeId="1106" r:id="rId873" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8657,7 +9225,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId785" name="A37">
+            <control shapeId="1107" r:id="rId874" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8679,7 +9247,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId786" name="A38">
+            <control shapeId="1108" r:id="rId875" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8701,7 +9269,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId787" name="A39">
+            <control shapeId="1109" r:id="rId876" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8723,7 +9291,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId788" name="A40">
+            <control shapeId="1110" r:id="rId877" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8745,7 +9313,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId789" name="A41">
+            <control shapeId="1111" r:id="rId878" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8767,7 +9335,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId790" name="A42">
+            <control shapeId="1112" r:id="rId879" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8789,7 +9357,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId791" name="A43">
+            <control shapeId="1113" r:id="rId880" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8811,7 +9379,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId792" name="A44">
+            <control shapeId="1114" r:id="rId881" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8833,7 +9401,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId793" name="A45">
+            <control shapeId="1115" r:id="rId882" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8853,6 +9421,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1116" r:id="rId883" name="A46">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>45</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>46</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1117" r:id="rId884" name="A47">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>46</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>47</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -321,6 +321,9 @@
     <t>MakeupUIForm.title</t>
   </si>
   <si>
+    <t>PrelevelUIForm.txtLevel</t>
+  </si>
+  <si>
     <t>TaskItem.infoTxt</t>
   </si>
 </sst>
@@ -536,6 +539,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -3947,6 +3954,194 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3963,93 +4158,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1071">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1072">
+            <xdr:cNvPr hidden="1" name="A1" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -4124,18 +4233,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1073">
+            <xdr:cNvPr hidden="1" name="A2" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -4210,18 +4319,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1074">
+            <xdr:cNvPr hidden="1" name="A3" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -4296,18 +4405,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1075">
+            <xdr:cNvPr hidden="1" name="A4" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -4382,18 +4491,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1076">
+            <xdr:cNvPr hidden="1" name="A5" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -4468,18 +4577,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1077">
+            <xdr:cNvPr hidden="1" name="A6" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -4554,18 +4663,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1078">
+            <xdr:cNvPr hidden="1" name="A7" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -4640,18 +4749,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1079">
+            <xdr:cNvPr hidden="1" name="A8" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -4726,18 +4835,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1080">
+            <xdr:cNvPr hidden="1" name="A9" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -4812,18 +4921,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1081">
+            <xdr:cNvPr hidden="1" name="A10" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -4898,18 +5007,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1082">
+            <xdr:cNvPr hidden="1" name="A11" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -4984,18 +5093,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1083">
+            <xdr:cNvPr hidden="1" name="A12" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -5070,18 +5179,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1084">
+            <xdr:cNvPr hidden="1" name="A13" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -5156,18 +5265,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1085">
+            <xdr:cNvPr hidden="1" name="A14" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -5242,18 +5351,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1086">
+            <xdr:cNvPr hidden="1" name="A15" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -5328,18 +5437,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1087">
+            <xdr:cNvPr hidden="1" name="A16" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -5414,18 +5523,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1088">
+            <xdr:cNvPr hidden="1" name="A17" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -5500,18 +5609,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1089">
+            <xdr:cNvPr hidden="1" name="A18" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -5586,18 +5695,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1090">
+            <xdr:cNvPr hidden="1" name="A19" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -5672,18 +5781,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1091">
+            <xdr:cNvPr hidden="1" name="A20" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -5758,18 +5867,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1092">
+            <xdr:cNvPr hidden="1" name="A21" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -5844,18 +5953,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1093">
+            <xdr:cNvPr hidden="1" name="A22" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -5930,18 +6039,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1094">
+            <xdr:cNvPr hidden="1" name="A23" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -6016,18 +6125,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1095">
+            <xdr:cNvPr hidden="1" name="A24" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -6102,18 +6211,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1096">
+            <xdr:cNvPr hidden="1" name="A25" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -6188,18 +6297,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1097">
+            <xdr:cNvPr hidden="1" name="A26" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -6274,18 +6383,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1098">
+            <xdr:cNvPr hidden="1" name="A27" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -6360,18 +6469,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1099">
+            <xdr:cNvPr hidden="1" name="A28" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -6446,18 +6555,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1100">
+            <xdr:cNvPr hidden="1" name="A29" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -6532,18 +6641,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1101">
+            <xdr:cNvPr hidden="1" name="A30" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -6618,18 +6727,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1102">
+            <xdr:cNvPr hidden="1" name="A31" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -6704,18 +6813,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1103">
+            <xdr:cNvPr hidden="1" name="A32" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -6790,18 +6899,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1104">
+            <xdr:cNvPr hidden="1" name="A33" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -6876,18 +6985,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1105">
+            <xdr:cNvPr hidden="1" name="A34" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -6962,18 +7071,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1106">
+            <xdr:cNvPr hidden="1" name="A35" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -7048,18 +7157,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1107">
+            <xdr:cNvPr hidden="1" name="A36" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -7134,18 +7243,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1108">
+            <xdr:cNvPr hidden="1" name="A37" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -7220,18 +7329,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1109">
+            <xdr:cNvPr hidden="1" name="A38" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -7306,18 +7415,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1110">
+            <xdr:cNvPr hidden="1" name="A39" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -7392,18 +7501,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1111">
+            <xdr:cNvPr hidden="1" name="A40" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -7478,18 +7587,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1112">
+            <xdr:cNvPr hidden="1" name="A41" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -7564,18 +7673,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1113">
+            <xdr:cNvPr hidden="1" name="A42" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -7650,18 +7759,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1114">
+            <xdr:cNvPr hidden="1" name="A43" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -7736,18 +7845,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1115">
+            <xdr:cNvPr hidden="1" name="A44" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -7822,18 +7931,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1116">
+            <xdr:cNvPr hidden="1" name="A45" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -7908,18 +8017,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1117">
+            <xdr:cNvPr hidden="1" name="A46" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -7988,12 +8097,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1118">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1118"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1119">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1119"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -8424,6 +8705,15 @@
         <v>81</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="1"/>
+      <c r="B48" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -8433,7 +8723,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId838" name="A1">
+            <control shapeId="1072" r:id="rId884" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8455,7 +8745,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId839" name="A2">
+            <control shapeId="1073" r:id="rId885" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8477,7 +8767,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId840" name="A3">
+            <control shapeId="1074" r:id="rId886" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8499,7 +8789,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId841" name="A4">
+            <control shapeId="1075" r:id="rId887" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8521,7 +8811,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId842" name="A5">
+            <control shapeId="1076" r:id="rId888" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8543,7 +8833,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId843" name="A6">
+            <control shapeId="1077" r:id="rId889" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8565,7 +8855,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId844" name="A7">
+            <control shapeId="1078" r:id="rId890" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8587,7 +8877,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId845" name="A8">
+            <control shapeId="1079" r:id="rId891" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8609,7 +8899,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId846" name="A9">
+            <control shapeId="1080" r:id="rId892" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8631,7 +8921,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId847" name="A10">
+            <control shapeId="1081" r:id="rId893" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8653,7 +8943,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId848" name="A11">
+            <control shapeId="1082" r:id="rId894" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8675,7 +8965,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId849" name="A12">
+            <control shapeId="1083" r:id="rId895" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8697,7 +8987,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId850" name="A13">
+            <control shapeId="1084" r:id="rId896" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8719,7 +9009,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId851" name="A14">
+            <control shapeId="1085" r:id="rId897" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8741,7 +9031,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId852" name="A15">
+            <control shapeId="1086" r:id="rId898" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8763,7 +9053,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId853" name="A16">
+            <control shapeId="1087" r:id="rId899" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8785,7 +9075,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId854" name="A17">
+            <control shapeId="1088" r:id="rId900" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8807,7 +9097,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId855" name="A18">
+            <control shapeId="1089" r:id="rId901" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8829,7 +9119,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId856" name="A19">
+            <control shapeId="1090" r:id="rId902" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8851,7 +9141,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId857" name="A20">
+            <control shapeId="1091" r:id="rId903" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8873,7 +9163,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId858" name="A21">
+            <control shapeId="1092" r:id="rId904" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8895,7 +9185,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId859" name="A22">
+            <control shapeId="1093" r:id="rId905" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8917,7 +9207,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId860" name="A23">
+            <control shapeId="1094" r:id="rId906" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8939,7 +9229,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId861" name="A24">
+            <control shapeId="1095" r:id="rId907" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8961,7 +9251,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId862" name="A25">
+            <control shapeId="1096" r:id="rId908" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8983,7 +9273,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId863" name="A26">
+            <control shapeId="1097" r:id="rId909" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9005,7 +9295,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId864" name="A27">
+            <control shapeId="1098" r:id="rId910" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9027,7 +9317,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId865" name="A28">
+            <control shapeId="1099" r:id="rId911" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9049,7 +9339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId866" name="A29">
+            <control shapeId="1100" r:id="rId912" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9071,7 +9361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId867" name="A30">
+            <control shapeId="1101" r:id="rId913" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9093,7 +9383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId868" name="A31">
+            <control shapeId="1102" r:id="rId914" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9115,7 +9405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId869" name="A32">
+            <control shapeId="1103" r:id="rId915" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9137,7 +9427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId870" name="A33">
+            <control shapeId="1104" r:id="rId916" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9159,7 +9449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId871" name="A34">
+            <control shapeId="1105" r:id="rId917" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9181,7 +9471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId872" name="A35">
+            <control shapeId="1106" r:id="rId918" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9203,7 +9493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId873" name="A36">
+            <control shapeId="1107" r:id="rId919" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9225,7 +9515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId874" name="A37">
+            <control shapeId="1108" r:id="rId920" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9247,7 +9537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId875" name="A38">
+            <control shapeId="1109" r:id="rId921" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9269,7 +9559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId876" name="A39">
+            <control shapeId="1110" r:id="rId922" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9291,7 +9581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId877" name="A40">
+            <control shapeId="1111" r:id="rId923" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9313,7 +9603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId878" name="A41">
+            <control shapeId="1112" r:id="rId924" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9335,7 +9625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId879" name="A42">
+            <control shapeId="1113" r:id="rId925" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9357,7 +9647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId880" name="A43">
+            <control shapeId="1114" r:id="rId926" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9379,7 +9669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId881" name="A44">
+            <control shapeId="1115" r:id="rId927" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9401,7 +9691,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId882" name="A45">
+            <control shapeId="1116" r:id="rId928" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9423,7 +9713,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId883" name="A46">
+            <control shapeId="1117" r:id="rId929" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9445,7 +9735,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId884" name="A47">
+            <control shapeId="1118" r:id="rId930" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9465,6 +9755,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1119" r:id="rId931" name="A48">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>47</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -321,6 +321,9 @@
     <t>MakeupUIForm.title</t>
   </si>
   <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
     <t>PrelevelUIForm.txtLevel</t>
   </si>
   <si>
@@ -543,6 +546,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -4142,6 +4149,198 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -4158,93 +4357,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1072">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1073">
+            <xdr:cNvPr hidden="1" name="A1" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -4319,18 +4432,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1074">
+            <xdr:cNvPr hidden="1" name="A2" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -4405,18 +4518,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1075">
+            <xdr:cNvPr hidden="1" name="A3" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -4491,18 +4604,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1076">
+            <xdr:cNvPr hidden="1" name="A4" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -4577,18 +4690,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1077">
+            <xdr:cNvPr hidden="1" name="A5" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -4663,18 +4776,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1078">
+            <xdr:cNvPr hidden="1" name="A6" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -4749,18 +4862,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1079">
+            <xdr:cNvPr hidden="1" name="A7" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -4835,18 +4948,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1080">
+            <xdr:cNvPr hidden="1" name="A8" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -4921,18 +5034,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1081">
+            <xdr:cNvPr hidden="1" name="A9" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -5007,18 +5120,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1082">
+            <xdr:cNvPr hidden="1" name="A10" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -5093,18 +5206,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1083">
+            <xdr:cNvPr hidden="1" name="A11" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -5179,18 +5292,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1084">
+            <xdr:cNvPr hidden="1" name="A12" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -5265,18 +5378,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1085">
+            <xdr:cNvPr hidden="1" name="A13" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -5351,18 +5464,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1086">
+            <xdr:cNvPr hidden="1" name="A14" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -5437,18 +5550,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1087">
+            <xdr:cNvPr hidden="1" name="A15" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -5523,18 +5636,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1088">
+            <xdr:cNvPr hidden="1" name="A16" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -5609,18 +5722,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1089">
+            <xdr:cNvPr hidden="1" name="A17" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -5695,18 +5808,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1090">
+            <xdr:cNvPr hidden="1" name="A18" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -5781,18 +5894,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1091">
+            <xdr:cNvPr hidden="1" name="A19" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -5867,18 +5980,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1092">
+            <xdr:cNvPr hidden="1" name="A20" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -5953,18 +6066,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1093">
+            <xdr:cNvPr hidden="1" name="A21" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -6039,18 +6152,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1094">
+            <xdr:cNvPr hidden="1" name="A22" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -6125,18 +6238,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1095">
+            <xdr:cNvPr hidden="1" name="A23" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -6211,18 +6324,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1096">
+            <xdr:cNvPr hidden="1" name="A24" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -6297,18 +6410,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1097">
+            <xdr:cNvPr hidden="1" name="A25" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -6383,18 +6496,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1098">
+            <xdr:cNvPr hidden="1" name="A26" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -6469,18 +6582,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1099">
+            <xdr:cNvPr hidden="1" name="A27" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -6555,18 +6668,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1100">
+            <xdr:cNvPr hidden="1" name="A28" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -6641,18 +6754,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1101">
+            <xdr:cNvPr hidden="1" name="A29" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -6727,18 +6840,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1102">
+            <xdr:cNvPr hidden="1" name="A30" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -6813,18 +6926,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1103">
+            <xdr:cNvPr hidden="1" name="A31" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -6899,18 +7012,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1104">
+            <xdr:cNvPr hidden="1" name="A32" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -6985,18 +7098,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1105">
+            <xdr:cNvPr hidden="1" name="A33" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -7071,18 +7184,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1106">
+            <xdr:cNvPr hidden="1" name="A34" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -7157,18 +7270,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1107">
+            <xdr:cNvPr hidden="1" name="A35" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -7243,18 +7356,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1108">
+            <xdr:cNvPr hidden="1" name="A36" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -7329,18 +7442,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1109">
+            <xdr:cNvPr hidden="1" name="A37" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -7415,18 +7528,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1110">
+            <xdr:cNvPr hidden="1" name="A38" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -7501,18 +7614,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1111">
+            <xdr:cNvPr hidden="1" name="A39" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -7587,18 +7700,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1112">
+            <xdr:cNvPr hidden="1" name="A40" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -7673,18 +7786,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1113">
+            <xdr:cNvPr hidden="1" name="A41" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -7759,18 +7872,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1114">
+            <xdr:cNvPr hidden="1" name="A42" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -7845,18 +7958,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1115">
+            <xdr:cNvPr hidden="1" name="A43" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -7931,18 +8044,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1116">
+            <xdr:cNvPr hidden="1" name="A44" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -8017,18 +8130,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1117">
+            <xdr:cNvPr hidden="1" name="A45" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -8103,18 +8216,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1118">
+            <xdr:cNvPr hidden="1" name="A46" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -8189,18 +8302,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1119">
+            <xdr:cNvPr hidden="1" name="A47" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -8269,12 +8382,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1120">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1120"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A49" id="1121">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1121"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -8714,6 +8999,15 @@
         <v>81</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1"/>
+      <c r="B49" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -8723,7 +9017,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId884" name="A1">
+            <control shapeId="1073" r:id="rId931" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8745,7 +9039,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId885" name="A2">
+            <control shapeId="1074" r:id="rId932" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8767,7 +9061,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId886" name="A3">
+            <control shapeId="1075" r:id="rId933" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8789,7 +9083,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId887" name="A4">
+            <control shapeId="1076" r:id="rId934" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8811,7 +9105,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId888" name="A5">
+            <control shapeId="1077" r:id="rId935" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8833,7 +9127,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId889" name="A6">
+            <control shapeId="1078" r:id="rId936" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8855,7 +9149,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId890" name="A7">
+            <control shapeId="1079" r:id="rId937" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8877,7 +9171,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId891" name="A8">
+            <control shapeId="1080" r:id="rId938" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8899,7 +9193,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId892" name="A9">
+            <control shapeId="1081" r:id="rId939" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8921,7 +9215,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId893" name="A10">
+            <control shapeId="1082" r:id="rId940" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8943,7 +9237,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId894" name="A11">
+            <control shapeId="1083" r:id="rId941" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8965,7 +9259,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId895" name="A12">
+            <control shapeId="1084" r:id="rId942" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8987,7 +9281,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId896" name="A13">
+            <control shapeId="1085" r:id="rId943" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9009,7 +9303,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId897" name="A14">
+            <control shapeId="1086" r:id="rId944" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9031,7 +9325,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId898" name="A15">
+            <control shapeId="1087" r:id="rId945" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9053,7 +9347,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId899" name="A16">
+            <control shapeId="1088" r:id="rId946" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9075,7 +9369,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId900" name="A17">
+            <control shapeId="1089" r:id="rId947" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9097,7 +9391,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId901" name="A18">
+            <control shapeId="1090" r:id="rId948" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9119,7 +9413,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId902" name="A19">
+            <control shapeId="1091" r:id="rId949" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9141,7 +9435,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId903" name="A20">
+            <control shapeId="1092" r:id="rId950" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9163,7 +9457,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId904" name="A21">
+            <control shapeId="1093" r:id="rId951" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9185,7 +9479,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId905" name="A22">
+            <control shapeId="1094" r:id="rId952" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9207,7 +9501,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId906" name="A23">
+            <control shapeId="1095" r:id="rId953" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9229,7 +9523,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId907" name="A24">
+            <control shapeId="1096" r:id="rId954" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9251,7 +9545,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId908" name="A25">
+            <control shapeId="1097" r:id="rId955" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9273,7 +9567,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId909" name="A26">
+            <control shapeId="1098" r:id="rId956" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9295,7 +9589,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId910" name="A27">
+            <control shapeId="1099" r:id="rId957" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9317,7 +9611,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId911" name="A28">
+            <control shapeId="1100" r:id="rId958" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9339,7 +9633,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId912" name="A29">
+            <control shapeId="1101" r:id="rId959" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9361,7 +9655,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId913" name="A30">
+            <control shapeId="1102" r:id="rId960" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9383,7 +9677,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId914" name="A31">
+            <control shapeId="1103" r:id="rId961" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9405,7 +9699,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId915" name="A32">
+            <control shapeId="1104" r:id="rId962" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9427,7 +9721,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId916" name="A33">
+            <control shapeId="1105" r:id="rId963" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9449,7 +9743,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId917" name="A34">
+            <control shapeId="1106" r:id="rId964" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9471,7 +9765,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId918" name="A35">
+            <control shapeId="1107" r:id="rId965" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9493,7 +9787,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId919" name="A36">
+            <control shapeId="1108" r:id="rId966" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9515,7 +9809,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId920" name="A37">
+            <control shapeId="1109" r:id="rId967" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9537,7 +9831,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId921" name="A38">
+            <control shapeId="1110" r:id="rId968" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9559,7 +9853,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId922" name="A39">
+            <control shapeId="1111" r:id="rId969" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9581,7 +9875,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId923" name="A40">
+            <control shapeId="1112" r:id="rId970" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9603,7 +9897,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId924" name="A41">
+            <control shapeId="1113" r:id="rId971" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9625,7 +9919,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId925" name="A42">
+            <control shapeId="1114" r:id="rId972" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9647,7 +9941,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId926" name="A43">
+            <control shapeId="1115" r:id="rId973" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9669,7 +9963,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId927" name="A44">
+            <control shapeId="1116" r:id="rId974" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9691,7 +9985,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId928" name="A45">
+            <control shapeId="1117" r:id="rId975" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9713,7 +10007,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId929" name="A46">
+            <control shapeId="1118" r:id="rId976" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9735,7 +10029,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId930" name="A47">
+            <control shapeId="1119" r:id="rId977" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9757,7 +10051,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId931" name="A48">
+            <control shapeId="1120" r:id="rId978" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9777,6 +10071,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1121" r:id="rId979" name="A49">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -55,7 +55,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+  <si>
+    <t>AddBallsUIForm.ballTxt</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AddBallsUIForm.continueTxt</t>
+  </si>
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -73,18 +82,6 @@
   </si>
   <si>
     <t>ふっきゅう</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.elimanateHit</t>
-  </si>
-  <si>
-    <t>消去する矢印を選択してください</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.LevelTxt</t>
-  </si>
-  <si>
-    <t>レベル＃0＃</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -189,6 +186,9 @@
     <t>プレイヤーの＃0＃パス（＃1＃）を祝い、＃2＃を獲得します。</t>
   </si>
   <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
     <t>Enteraccountnumber</t>
   </si>
   <si>
@@ -249,6 +249,15 @@
     <t>現金化要件を完了します。</t>
   </si>
   <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
@@ -291,6 +300,12 @@
     <t>支払情報の保存に成功しました</t>
   </si>
   <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.leveltxt</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
@@ -300,10 +315,13 @@
     <t>makeupInfoHint1</t>
   </si>
   <si>
-    <t/>
+    <t>makeupInfoHint2</t>
   </si>
   <si>
-    <t>makeupInfoHint2</t>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
   </si>
   <si>
     <t>MakeUpStep1</t>
@@ -318,13 +336,37 @@
     <t>再収集＃0＃</t>
   </si>
   <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
     <t>MakeupUIForm.title</t>
   </si>
   <si>
     <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
     <t>PrelevelUIForm.txtLevel</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.privacy</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.quit</t>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -439,7 +481,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,15 +529,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -531,7 +573,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,22 +581,86 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -4341,6 +4447,1650 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -4357,1469 +6107,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1073">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1074">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1075">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1076">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1077">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1078">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1079">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1080">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1081">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1082">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1083">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1084">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1085">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1086">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1087">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1088">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1089">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1090">
+            <xdr:cNvPr hidden="1" name="A1" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -5894,18 +6182,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1091">
+            <xdr:cNvPr hidden="1" name="A2" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -5980,18 +6268,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1092">
+            <xdr:cNvPr hidden="1" name="A3" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -6066,18 +6354,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1093">
+            <xdr:cNvPr hidden="1" name="A4" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -6152,18 +6440,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1094">
+            <xdr:cNvPr hidden="1" name="A5" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -6238,18 +6526,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1095">
+            <xdr:cNvPr hidden="1" name="A6" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -6324,18 +6612,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1096">
+            <xdr:cNvPr hidden="1" name="A7" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -6410,18 +6698,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1097">
+            <xdr:cNvPr hidden="1" name="A8" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -6496,18 +6784,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1098">
+            <xdr:cNvPr hidden="1" name="A9" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -6582,18 +6870,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1099">
+            <xdr:cNvPr hidden="1" name="A10" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -6668,18 +6956,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1100">
+            <xdr:cNvPr hidden="1" name="A11" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -6754,18 +7042,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1101">
+            <xdr:cNvPr hidden="1" name="A12" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -6840,18 +7128,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1102">
+            <xdr:cNvPr hidden="1" name="A13" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -6926,18 +7214,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1103">
+            <xdr:cNvPr hidden="1" name="A14" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -7012,18 +7300,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1104">
+            <xdr:cNvPr hidden="1" name="A15" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -7098,18 +7386,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1105">
+            <xdr:cNvPr hidden="1" name="A16" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -7184,18 +7472,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1106">
+            <xdr:cNvPr hidden="1" name="A17" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -7270,18 +7558,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1107">
+            <xdr:cNvPr hidden="1" name="A18" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -7356,18 +7644,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1108">
+            <xdr:cNvPr hidden="1" name="A19" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -7442,18 +7730,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1109">
+            <xdr:cNvPr hidden="1" name="A20" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -7528,18 +7816,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1110">
+            <xdr:cNvPr hidden="1" name="A21" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -7614,18 +7902,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1111">
+            <xdr:cNvPr hidden="1" name="A22" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -7700,18 +7988,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1112">
+            <xdr:cNvPr hidden="1" name="A23" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -7786,18 +8074,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1113">
+            <xdr:cNvPr hidden="1" name="A24" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -7872,18 +8160,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1114">
+            <xdr:cNvPr hidden="1" name="A25" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -7958,18 +8246,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1115">
+            <xdr:cNvPr hidden="1" name="A26" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -8044,18 +8332,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1116">
+            <xdr:cNvPr hidden="1" name="A27" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -8130,18 +8418,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1117">
+            <xdr:cNvPr hidden="1" name="A28" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -8216,18 +8504,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1118">
+            <xdr:cNvPr hidden="1" name="A29" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -8302,18 +8590,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1119">
+            <xdr:cNvPr hidden="1" name="A30" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -8388,18 +8676,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1120">
+            <xdr:cNvPr hidden="1" name="A31" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1120"/>
@@ -8474,18 +8762,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1121">
+            <xdr:cNvPr hidden="1" name="A32" id="1121">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1121"/>
@@ -8554,12 +8842,2850 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A33" id="1122">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1122"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A34" id="1123">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1123"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A35" id="1124">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1124"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A36" id="1125">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1125"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A37" id="1126">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1126"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A38" id="1127">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1127"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A39" id="1128">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1128"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>40</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A40" id="1129">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1129"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>40</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A41" id="1130">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1130"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A42" id="1131">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1131"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A43" id="1132">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1132"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A44" id="1133">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1133"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A45" id="1134">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1134"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A46" id="1135">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1135"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1136">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1136"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1137">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1137"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A49" id="1138">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1138"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A50" id="1139">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1139"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A51" id="1140">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1140"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A52" id="1141">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1141"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A53" id="1142">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1142"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A54" id="1143">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1143"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A55" id="1144">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1144"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A56" id="1145">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1145"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A57" id="1146">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1146"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A58" id="1147">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1147"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A59" id="1148">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1148"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A60" id="1149">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1149"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A61" id="1150">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1150"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A62" id="1151">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1151"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A63" id="1152">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1152"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A64" id="1153">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1153"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A65" id="1154">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1154"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -8582,430 +11708,574 @@
         <v>2</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="0" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="0" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1"/>
       <c r="B46" s="0" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1"/>
       <c r="B47" s="0" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="0" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1"/>
+      <c r="B50" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1"/>
+      <c r="B51" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1"/>
+      <c r="B52" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="0" t="s">
-        <v>81</v>
+    </row>
+    <row r="53">
+      <c r="A53" s="1"/>
+      <c r="B53" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1"/>
+      <c r="B54" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1"/>
+      <c r="B55" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1"/>
+      <c r="B56" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1"/>
+      <c r="B57" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1"/>
+      <c r="B58" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1"/>
+      <c r="B59" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1"/>
+      <c r="B60" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1"/>
+      <c r="B61" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1"/>
+      <c r="B62" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1"/>
+      <c r="B63" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1"/>
+      <c r="B64" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1"/>
+      <c r="B65" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9017,7 +12287,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId931" name="A1">
+            <control shapeId="1090" r:id="rId1335" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9039,7 +12309,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId932" name="A2">
+            <control shapeId="1091" r:id="rId1336" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9061,7 +12331,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId933" name="A3">
+            <control shapeId="1092" r:id="rId1337" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9083,7 +12353,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId934" name="A4">
+            <control shapeId="1093" r:id="rId1338" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9105,7 +12375,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId935" name="A5">
+            <control shapeId="1094" r:id="rId1339" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9127,7 +12397,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId936" name="A6">
+            <control shapeId="1095" r:id="rId1340" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9149,7 +12419,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId937" name="A7">
+            <control shapeId="1096" r:id="rId1341" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9171,7 +12441,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId938" name="A8">
+            <control shapeId="1097" r:id="rId1342" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9193,7 +12463,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId939" name="A9">
+            <control shapeId="1098" r:id="rId1343" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9215,7 +12485,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId940" name="A10">
+            <control shapeId="1099" r:id="rId1344" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9237,7 +12507,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId941" name="A11">
+            <control shapeId="1100" r:id="rId1345" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9259,7 +12529,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId942" name="A12">
+            <control shapeId="1101" r:id="rId1346" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9281,7 +12551,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId943" name="A13">
+            <control shapeId="1102" r:id="rId1347" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9303,7 +12573,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId944" name="A14">
+            <control shapeId="1103" r:id="rId1348" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9325,7 +12595,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId945" name="A15">
+            <control shapeId="1104" r:id="rId1349" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9347,7 +12617,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId946" name="A16">
+            <control shapeId="1105" r:id="rId1350" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9369,7 +12639,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId947" name="A17">
+            <control shapeId="1106" r:id="rId1351" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9391,7 +12661,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId948" name="A18">
+            <control shapeId="1107" r:id="rId1352" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9413,7 +12683,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId949" name="A19">
+            <control shapeId="1108" r:id="rId1353" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9435,7 +12705,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId950" name="A20">
+            <control shapeId="1109" r:id="rId1354" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9457,7 +12727,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId951" name="A21">
+            <control shapeId="1110" r:id="rId1355" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9479,7 +12749,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId952" name="A22">
+            <control shapeId="1111" r:id="rId1356" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9501,7 +12771,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId953" name="A23">
+            <control shapeId="1112" r:id="rId1357" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9523,7 +12793,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId954" name="A24">
+            <control shapeId="1113" r:id="rId1358" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9545,7 +12815,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId955" name="A25">
+            <control shapeId="1114" r:id="rId1359" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9567,7 +12837,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId956" name="A26">
+            <control shapeId="1115" r:id="rId1360" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9589,7 +12859,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId957" name="A27">
+            <control shapeId="1116" r:id="rId1361" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9611,7 +12881,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId958" name="A28">
+            <control shapeId="1117" r:id="rId1362" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9633,7 +12903,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId959" name="A29">
+            <control shapeId="1118" r:id="rId1363" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9655,7 +12925,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId960" name="A30">
+            <control shapeId="1119" r:id="rId1364" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9677,7 +12947,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId961" name="A31">
+            <control shapeId="1120" r:id="rId1365" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9699,7 +12969,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId962" name="A32">
+            <control shapeId="1121" r:id="rId1366" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9721,7 +12991,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId963" name="A33">
+            <control shapeId="1122" r:id="rId1367" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9743,7 +13013,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId964" name="A34">
+            <control shapeId="1123" r:id="rId1368" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9765,7 +13035,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId965" name="A35">
+            <control shapeId="1124" r:id="rId1369" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9787,7 +13057,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId966" name="A36">
+            <control shapeId="1125" r:id="rId1370" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9809,7 +13079,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId967" name="A37">
+            <control shapeId="1126" r:id="rId1371" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9831,7 +13101,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId968" name="A38">
+            <control shapeId="1127" r:id="rId1372" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9853,7 +13123,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId969" name="A39">
+            <control shapeId="1128" r:id="rId1373" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9875,7 +13145,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId970" name="A40">
+            <control shapeId="1129" r:id="rId1374" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9897,7 +13167,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId971" name="A41">
+            <control shapeId="1130" r:id="rId1375" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9919,7 +13189,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId972" name="A42">
+            <control shapeId="1131" r:id="rId1376" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9941,7 +13211,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId973" name="A43">
+            <control shapeId="1132" r:id="rId1377" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9963,7 +13233,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId974" name="A44">
+            <control shapeId="1133" r:id="rId1378" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9985,7 +13255,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId975" name="A45">
+            <control shapeId="1134" r:id="rId1379" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10007,7 +13277,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId976" name="A46">
+            <control shapeId="1135" r:id="rId1380" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10029,7 +13299,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId977" name="A47">
+            <control shapeId="1136" r:id="rId1381" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10051,7 +13321,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId978" name="A48">
+            <control shapeId="1137" r:id="rId1382" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10073,7 +13343,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId979" name="A49">
+            <control shapeId="1138" r:id="rId1383" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10093,6 +13363,358 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1139" r:id="rId1384" name="A50">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1140" r:id="rId1385" name="A51">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1141" r:id="rId1386" name="A52">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1142" r:id="rId1387" name="A53">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1143" r:id="rId1388" name="A54">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1144" r:id="rId1389" name="A55">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1145" r:id="rId1390" name="A56">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1146" r:id="rId1391" name="A57">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1147" r:id="rId1392" name="A58">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1148" r:id="rId1393" name="A59">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1149" r:id="rId1394" name="A60">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1150" r:id="rId1395" name="A61">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1151" r:id="rId1396" name="A62">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1152" r:id="rId1397" name="A63">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1153" r:id="rId1398" name="A64">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1154" r:id="rId1399" name="A65">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -186,6 +186,9 @@
     <t>プレイヤーの＃0＃パス（＃1＃）を祝い、＃2＃を獲得します。</t>
   </si>
   <si>
+    <t>claim</t>
+  </si>
+  <si>
     <t>CoinRewardUIForm.titletxt</t>
   </si>
   <si>
@@ -300,10 +303,13 @@
     <t>支払情報の保存に成功しました</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
-    <t>LevelCompleteUIForm.leveltxt</t>
+    <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
     <t>MakeUpFail</t>
@@ -349,9 +355,6 @@
   </si>
   <si>
     <t>PcardGiftUIForm.desc</t>
-  </si>
-  <si>
-    <t>PrelevelUIForm.txtLevel</t>
   </si>
   <si>
     <t>QuitConfirmUIForm.desc</t>
@@ -485,7 +488,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
@@ -529,7 +532,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -541,7 +544,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
@@ -573,7 +576,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
@@ -581,11 +584,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,27 +600,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
@@ -664,6 +667,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -678,6 +685,1066 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -6107,179 +7174,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1090">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1091">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1092">
+            <xdr:cNvPr hidden="1" name="A1" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -6354,18 +7249,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1093">
+            <xdr:cNvPr hidden="1" name="A2" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -6440,18 +7335,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1094">
+            <xdr:cNvPr hidden="1" name="A3" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -6526,18 +7421,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1095">
+            <xdr:cNvPr hidden="1" name="A4" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -6612,18 +7507,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1096">
+            <xdr:cNvPr hidden="1" name="A5" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -6698,18 +7593,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1097">
+            <xdr:cNvPr hidden="1" name="A6" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -6784,18 +7679,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1098">
+            <xdr:cNvPr hidden="1" name="A7" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -6870,18 +7765,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1099">
+            <xdr:cNvPr hidden="1" name="A8" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -6956,18 +7851,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1100">
+            <xdr:cNvPr hidden="1" name="A9" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -7042,18 +7937,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1101">
+            <xdr:cNvPr hidden="1" name="A10" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -7128,18 +8023,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1102">
+            <xdr:cNvPr hidden="1" name="A11" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -7214,18 +8109,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1103">
+            <xdr:cNvPr hidden="1" name="A12" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -7300,18 +8195,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1104">
+            <xdr:cNvPr hidden="1" name="A13" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -7386,18 +8281,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1105">
+            <xdr:cNvPr hidden="1" name="A14" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -7472,18 +8367,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1106">
+            <xdr:cNvPr hidden="1" name="A15" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -7558,18 +8453,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1107">
+            <xdr:cNvPr hidden="1" name="A16" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -7644,18 +8539,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1108">
+            <xdr:cNvPr hidden="1" name="A17" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -7730,18 +8625,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1109">
+            <xdr:cNvPr hidden="1" name="A18" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -7816,18 +8711,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1110">
+            <xdr:cNvPr hidden="1" name="A19" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -7902,18 +8797,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1111">
+            <xdr:cNvPr hidden="1" name="A20" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -7988,18 +8883,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1112">
+            <xdr:cNvPr hidden="1" name="A21" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -8074,18 +8969,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1113">
+            <xdr:cNvPr hidden="1" name="A22" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -8160,18 +9055,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1114">
+            <xdr:cNvPr hidden="1" name="A23" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -8246,18 +9141,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1115">
+            <xdr:cNvPr hidden="1" name="A24" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -8332,18 +9227,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1116">
+            <xdr:cNvPr hidden="1" name="A25" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -8418,18 +9313,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1117">
+            <xdr:cNvPr hidden="1" name="A26" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -8504,18 +9399,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1118">
+            <xdr:cNvPr hidden="1" name="A27" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -8590,18 +9485,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1119">
+            <xdr:cNvPr hidden="1" name="A28" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -8676,18 +9571,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1120">
+            <xdr:cNvPr hidden="1" name="A29" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1120"/>
@@ -8762,18 +9657,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1121">
+            <xdr:cNvPr hidden="1" name="A30" id="1121">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1121"/>
@@ -8848,18 +9743,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1122">
+            <xdr:cNvPr hidden="1" name="A31" id="1122">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1122"/>
@@ -8934,18 +9829,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1123">
+            <xdr:cNvPr hidden="1" name="A32" id="1123">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1123"/>
@@ -9020,18 +9915,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1124">
+            <xdr:cNvPr hidden="1" name="A33" id="1124">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1124"/>
@@ -9106,18 +10001,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1125">
+            <xdr:cNvPr hidden="1" name="A34" id="1125">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1125"/>
@@ -9192,18 +10087,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1126">
+            <xdr:cNvPr hidden="1" name="A35" id="1126">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1126"/>
@@ -9278,18 +10173,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1127">
+            <xdr:cNvPr hidden="1" name="A36" id="1127">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1127"/>
@@ -9364,18 +10259,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1128">
+            <xdr:cNvPr hidden="1" name="A37" id="1128">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1128"/>
@@ -9450,18 +10345,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1129">
+            <xdr:cNvPr hidden="1" name="A38" id="1129">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1129"/>
@@ -9536,18 +10431,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1130">
+            <xdr:cNvPr hidden="1" name="A39" id="1130">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1130"/>
@@ -9622,18 +10517,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1131">
+            <xdr:cNvPr hidden="1" name="A40" id="1131">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1131"/>
@@ -9708,18 +10603,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1132">
+            <xdr:cNvPr hidden="1" name="A41" id="1132">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1132"/>
@@ -9794,18 +10689,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1133">
+            <xdr:cNvPr hidden="1" name="A42" id="1133">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1133"/>
@@ -9880,18 +10775,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1134">
+            <xdr:cNvPr hidden="1" name="A43" id="1134">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1134"/>
@@ -9966,18 +10861,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1135">
+            <xdr:cNvPr hidden="1" name="A44" id="1135">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1135"/>
@@ -10052,18 +10947,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1136">
+            <xdr:cNvPr hidden="1" name="A45" id="1136">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1136"/>
@@ -10138,18 +11033,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1137">
+            <xdr:cNvPr hidden="1" name="A46" id="1137">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1137"/>
@@ -10224,18 +11119,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1138">
+            <xdr:cNvPr hidden="1" name="A47" id="1138">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1138"/>
@@ -10310,18 +11205,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1139">
+            <xdr:cNvPr hidden="1" name="A48" id="1139">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1139"/>
@@ -10396,18 +11291,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1140">
+            <xdr:cNvPr hidden="1" name="A49" id="1140">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1140"/>
@@ -10482,18 +11377,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1141">
+            <xdr:cNvPr hidden="1" name="A50" id="1141">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1141"/>
@@ -10568,18 +11463,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1142">
+            <xdr:cNvPr hidden="1" name="A51" id="1142">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1142"/>
@@ -10654,18 +11549,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1143">
+            <xdr:cNvPr hidden="1" name="A52" id="1143">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1143"/>
@@ -10740,18 +11635,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1144">
+            <xdr:cNvPr hidden="1" name="A53" id="1144">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1144"/>
@@ -10826,18 +11721,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1145">
+            <xdr:cNvPr hidden="1" name="A54" id="1145">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1145"/>
@@ -10912,18 +11807,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1146">
+            <xdr:cNvPr hidden="1" name="A55" id="1146">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1146"/>
@@ -10998,18 +11893,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1147">
+            <xdr:cNvPr hidden="1" name="A56" id="1147">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1147"/>
@@ -11084,18 +11979,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1148">
+            <xdr:cNvPr hidden="1" name="A57" id="1148">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1148"/>
@@ -11170,18 +12065,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1149">
+            <xdr:cNvPr hidden="1" name="A58" id="1149">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1149"/>
@@ -11256,18 +12151,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1150">
+            <xdr:cNvPr hidden="1" name="A59" id="1150">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1150"/>
@@ -11342,18 +12237,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1151">
+            <xdr:cNvPr hidden="1" name="A60" id="1151">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1151"/>
@@ -11428,18 +12323,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1152">
+            <xdr:cNvPr hidden="1" name="A61" id="1152">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1152"/>
@@ -11514,18 +12409,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>64</xdr:row>
+          <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1153">
+            <xdr:cNvPr hidden="1" name="A62" id="1153">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1153"/>
@@ -11600,18 +12495,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>64</xdr:row>
+          <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>65</xdr:row>
+          <xdr:row>63</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1154">
+            <xdr:cNvPr hidden="1" name="A63" id="1154">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1154"/>
@@ -11680,12 +12575,270 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A64" id="1155">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1155"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A65" id="1156">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1156"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A66" id="1157">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1157"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -11915,97 +13068,97 @@
         <v>44</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36">
@@ -12032,70 +13185,70 @@
         <v>67</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
@@ -12113,13 +13266,13 @@
         <v>83</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>1</v>
@@ -12128,10 +13281,10 @@
     <row r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
@@ -12158,34 +13311,34 @@
         <v>89</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1"/>
       <c r="B53" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1"/>
       <c r="B54" s="0" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1"/>
       <c r="B55" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56">
@@ -12278,6 +13431,15 @@
         <v>1</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="1"/>
+      <c r="B66" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -12287,7 +13449,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1335" name="A1">
+            <control shapeId="1092" r:id="rId1596" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12309,7 +13471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1336" name="A2">
+            <control shapeId="1093" r:id="rId1597" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12331,7 +13493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1337" name="A3">
+            <control shapeId="1094" r:id="rId1598" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12353,7 +13515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1338" name="A4">
+            <control shapeId="1095" r:id="rId1599" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12375,7 +13537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1339" name="A5">
+            <control shapeId="1096" r:id="rId1600" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12397,7 +13559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1340" name="A6">
+            <control shapeId="1097" r:id="rId1601" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12419,7 +13581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1341" name="A7">
+            <control shapeId="1098" r:id="rId1602" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12441,7 +13603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1342" name="A8">
+            <control shapeId="1099" r:id="rId1603" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12463,7 +13625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1343" name="A9">
+            <control shapeId="1100" r:id="rId1604" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12485,7 +13647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1344" name="A10">
+            <control shapeId="1101" r:id="rId1605" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12507,7 +13669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1345" name="A11">
+            <control shapeId="1102" r:id="rId1606" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12529,7 +13691,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1346" name="A12">
+            <control shapeId="1103" r:id="rId1607" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12551,7 +13713,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1347" name="A13">
+            <control shapeId="1104" r:id="rId1608" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12573,7 +13735,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1348" name="A14">
+            <control shapeId="1105" r:id="rId1609" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12595,7 +13757,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1349" name="A15">
+            <control shapeId="1106" r:id="rId1610" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12617,7 +13779,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1350" name="A16">
+            <control shapeId="1107" r:id="rId1611" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12639,7 +13801,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1351" name="A17">
+            <control shapeId="1108" r:id="rId1612" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12661,7 +13823,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1352" name="A18">
+            <control shapeId="1109" r:id="rId1613" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12683,7 +13845,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1353" name="A19">
+            <control shapeId="1110" r:id="rId1614" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12705,7 +13867,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1354" name="A20">
+            <control shapeId="1111" r:id="rId1615" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12727,7 +13889,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1355" name="A21">
+            <control shapeId="1112" r:id="rId1616" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12749,7 +13911,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1356" name="A22">
+            <control shapeId="1113" r:id="rId1617" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12771,7 +13933,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1357" name="A23">
+            <control shapeId="1114" r:id="rId1618" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12793,7 +13955,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1358" name="A24">
+            <control shapeId="1115" r:id="rId1619" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12815,7 +13977,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1359" name="A25">
+            <control shapeId="1116" r:id="rId1620" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12837,7 +13999,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1360" name="A26">
+            <control shapeId="1117" r:id="rId1621" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12859,7 +14021,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1361" name="A27">
+            <control shapeId="1118" r:id="rId1622" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12881,7 +14043,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1362" name="A28">
+            <control shapeId="1119" r:id="rId1623" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12903,7 +14065,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1363" name="A29">
+            <control shapeId="1120" r:id="rId1624" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12925,7 +14087,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1364" name="A30">
+            <control shapeId="1121" r:id="rId1625" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12947,7 +14109,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1365" name="A31">
+            <control shapeId="1122" r:id="rId1626" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12969,7 +14131,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1366" name="A32">
+            <control shapeId="1123" r:id="rId1627" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12991,7 +14153,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId1367" name="A33">
+            <control shapeId="1124" r:id="rId1628" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13013,7 +14175,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId1368" name="A34">
+            <control shapeId="1125" r:id="rId1629" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13035,7 +14197,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId1369" name="A35">
+            <control shapeId="1126" r:id="rId1630" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13057,7 +14219,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId1370" name="A36">
+            <control shapeId="1127" r:id="rId1631" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13079,7 +14241,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId1371" name="A37">
+            <control shapeId="1128" r:id="rId1632" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13101,7 +14263,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId1372" name="A38">
+            <control shapeId="1129" r:id="rId1633" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13123,7 +14285,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId1373" name="A39">
+            <control shapeId="1130" r:id="rId1634" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13145,7 +14307,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId1374" name="A40">
+            <control shapeId="1131" r:id="rId1635" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13167,7 +14329,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId1375" name="A41">
+            <control shapeId="1132" r:id="rId1636" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13189,7 +14351,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId1376" name="A42">
+            <control shapeId="1133" r:id="rId1637" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13211,7 +14373,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId1377" name="A43">
+            <control shapeId="1134" r:id="rId1638" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13233,7 +14395,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId1378" name="A44">
+            <control shapeId="1135" r:id="rId1639" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13255,7 +14417,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId1379" name="A45">
+            <control shapeId="1136" r:id="rId1640" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13277,7 +14439,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId1380" name="A46">
+            <control shapeId="1137" r:id="rId1641" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13299,7 +14461,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId1381" name="A47">
+            <control shapeId="1138" r:id="rId1642" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13321,7 +14483,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId1382" name="A48">
+            <control shapeId="1139" r:id="rId1643" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13343,7 +14505,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId1383" name="A49">
+            <control shapeId="1140" r:id="rId1644" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13365,7 +14527,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId1384" name="A50">
+            <control shapeId="1141" r:id="rId1645" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13387,7 +14549,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId1385" name="A51">
+            <control shapeId="1142" r:id="rId1646" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13409,7 +14571,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId1386" name="A52">
+            <control shapeId="1143" r:id="rId1647" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13431,7 +14593,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId1387" name="A53">
+            <control shapeId="1144" r:id="rId1648" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13453,7 +14615,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId1388" name="A54">
+            <control shapeId="1145" r:id="rId1649" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13475,7 +14637,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId1389" name="A55">
+            <control shapeId="1146" r:id="rId1650" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13497,7 +14659,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId1390" name="A56">
+            <control shapeId="1147" r:id="rId1651" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13519,7 +14681,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId1391" name="A57">
+            <control shapeId="1148" r:id="rId1652" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13541,7 +14703,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId1392" name="A58">
+            <control shapeId="1149" r:id="rId1653" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13563,7 +14725,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId1393" name="A59">
+            <control shapeId="1150" r:id="rId1654" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13585,7 +14747,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId1394" name="A60">
+            <control shapeId="1151" r:id="rId1655" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13607,7 +14769,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId1395" name="A61">
+            <control shapeId="1152" r:id="rId1656" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13629,7 +14791,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId1396" name="A62">
+            <control shapeId="1153" r:id="rId1657" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13651,7 +14813,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId1397" name="A63">
+            <control shapeId="1154" r:id="rId1658" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13673,7 +14835,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId1398" name="A64">
+            <control shapeId="1155" r:id="rId1659" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13695,7 +14857,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId1399" name="A65">
+            <control shapeId="1156" r:id="rId1660" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13715,6 +14877,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1157" r:id="rId1661" name="A66">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -11,61 +11,21 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Anonymous</d:author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">勾选锁定此行,锁定后将强制保留</t>
-        </d:r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">多语言Key</t>
-        </d:r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">多语言Value, 当值为空时, [一键翻译]会自动填充Value值</t>
-        </d:r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
   <si>
-    <t/>
+    <t>ボール+5個</t>
   </si>
   <si>
     <t>AddBallsUIForm.continueTxt</t>
   </si>
   <si>
+    <t>続けますか？</t>
+  </si>
+  <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
   <si>
@@ -75,13 +35,13 @@
     <t>ArrowMazeOverUIForm.restart</t>
   </si>
   <si>
-    <t>再起動</t>
+    <t>やり直す</t>
   </si>
   <si>
     <t>ArrowMazeOverUIForm.Revive</t>
   </si>
   <si>
-    <t>ふっきゅう</t>
+    <t>復活</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -93,7 +53,7 @@
     <t>ArrowRewardDialogUIForm.claim</t>
   </si>
   <si>
-    <t>クレーム</t>
+    <t>受け取る</t>
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.Continue</t>
@@ -105,40 +65,43 @@
     <t>ArrowRewardDialogUIForm.NextLevel</t>
   </si>
   <si>
-    <t>新境地</t>
+    <t>次のステージ</t>
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.titletxt</t>
   </si>
   <si>
-    <t>おめでとう</t>
+    <t>コンボ報酬</t>
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.winTitle</t>
   </si>
   <si>
-    <t>水平完了</t>
+    <t>ステージクリア</t>
   </si>
   <si>
     <t>ArrowRewardUIForm.titletxt</t>
   </si>
   <si>
+    <t>おめでとう！</t>
+  </si>
+  <si>
     <t>ArrowSettingController.OFF</t>
   </si>
   <si>
-    <t>関</t>
+    <t>オフ</t>
   </si>
   <si>
     <t>ArrowSettingController.ON</t>
   </si>
   <si>
-    <t>上</t>
+    <t>オン</t>
   </si>
   <si>
     <t>ArrowSettingDialog.Home</t>
   </si>
   <si>
-    <t>家（いえ）</t>
+    <t>ホーム</t>
   </si>
   <si>
     <t>ArrowSettingDialog.Music</t>
@@ -153,13 +116,13 @@
     <t>ArrowSettingDialog.Resume</t>
   </si>
   <si>
-    <t>履歴書</t>
+    <t>再開</t>
   </si>
   <si>
     <t>ArrowSettingDialog.Sound</t>
   </si>
   <si>
-    <t>声</t>
+    <t>サウンド</t>
   </si>
   <si>
     <t>ArrowSettingDialog.Text_Title</t>
@@ -177,13 +140,13 @@
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
-    <t>両替</t>
+    <t>交換</t>
   </si>
   <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
   </si>
   <si>
-    <t>プレイヤーの＃0＃パス（＃1＃）を祝い、＃2＃を獲得します。</t>
+    <t>プレイヤー{0}さん、({1})のクリアと{2}の獲得、おめでとうございます！</t>
   </si>
   <si>
     <t>claim</t>
@@ -195,61 +158,61 @@
     <t>Enteraccountnumber</t>
   </si>
   <si>
-    <t>アカウントを入力</t>
+    <t>口座を入力</t>
   </si>
   <si>
     <t>EnterCPF</t>
   </si>
   <si>
-    <t>CPFへ</t>
+    <t>CPFを入力</t>
   </si>
   <si>
     <t>Enteremail</t>
   </si>
   <si>
-    <t>Eメールの確認</t>
+    <t>メールアドレスを確認</t>
   </si>
   <si>
     <t>EnterFullName</t>
   </si>
   <si>
-    <t>フルネームを入力</t>
+    <t>氏名を入力</t>
   </si>
   <si>
     <t>EnterPayPalaccount</t>
   </si>
   <si>
-    <t>PayPalアカウントの入力</t>
+    <t>PayPalアカウントを入力</t>
   </si>
   <si>
     <t>GuidTxt1</t>
   </si>
   <si>
-    <t>クリックして移動</t>
+    <t>タップして移動</t>
   </si>
   <si>
     <t>GuidTxt3</t>
   </si>
   <si>
-    <t xml:space="preserve">ここをクリックして現金化 </t>
+    <t xml:space="preserve">ここをタップして出金 </t>
   </si>
   <si>
     <t>GuidTxt4</t>
   </si>
   <si>
-    <t>指を広げてスケール</t>
+    <t>指を広げて拡大</t>
   </si>
   <si>
     <t>GuidTxt5</t>
   </si>
   <si>
-    <t xml:space="preserve">現在の残高をここに表示してください。 </t>
+    <t xml:space="preserve">現在の残高はこちらで確認できます。 </t>
   </si>
   <si>
     <t>GuidTxt6</t>
   </si>
   <si>
-    <t>現金化要件を完了します。</t>
+    <t>条件を達成すると出金できます。</t>
   </si>
   <si>
     <t>HallTabUIForm.home</t>
@@ -261,10 +224,13 @@
     <t>HallTabUIForm.task</t>
   </si>
   <si>
+    <t>タスク</t>
+  </si>
+  <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
-    <t>有効な電子メールアドレスを入力してください</t>
+    <t>有効なメールアドレスを入力してください</t>
   </si>
   <si>
     <t>InfoErrTips2</t>
@@ -276,93 +242,132 @@
     <t>InfoErrTips3</t>
   </si>
   <si>
-    <t>PayPalアカウントは有効な電子メールでなければなりません</t>
+    <t>PayPalアカウントには有効なメールアドレスが必要です</t>
   </si>
   <si>
     <t>InfoErrTips4</t>
   </si>
   <si>
-    <t>フルネームを入力してください</t>
+    <t>氏名を入力してください</t>
   </si>
   <si>
     <t>InfoErrTips5</t>
   </si>
   <si>
-    <t>アカウントを入力してください</t>
+    <t>口座番号を入力してください</t>
   </si>
   <si>
     <t>InfoErrTips6</t>
   </si>
   <si>
-    <t>支払い方法を選択してください</t>
+    <t>お支払い方法を選択してください</t>
   </si>
   <si>
     <t>InfoErrTips7</t>
   </si>
   <si>
-    <t>支払情報の保存に成功しました</t>
+    <t>お支払い情報を保存しました</t>
   </si>
   <si>
     <t>level</t>
   </si>
   <si>
+    <t>ステージ{0}</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
+    <t>次へ</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
-    <t>交換に失敗して残念です。</t>
+    <t>申し訳ありません。交換に失敗しました。</t>
   </si>
   <si>
     <t>makeupInfoHint1</t>
   </si>
   <si>
+    <t>2回入力したPayPalアカウントが一致していることを確認してください。</t>
+  </si>
+  <si>
     <t>makeupInfoHint2</t>
   </si>
   <si>
+    <t>正しい形式でメールアドレスを入力してください。</t>
+  </si>
+  <si>
     <t>MakeupPaymentUIForm.desc</t>
   </si>
   <si>
+    <t>出金処理中</t>
+  </si>
+  <si>
     <t>MakeupPaymentUIForm.titletxt</t>
   </si>
   <si>
+    <t>お支払い方法</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
-    <t>レベル＃0＃による引き出し</t>
+    <t>ステージ{0}をクリアすると出金できます</t>
   </si>
   <si>
     <t>MakeUpStep2</t>
   </si>
   <si>
-    <t>再収集＃0＃</t>
+    <t>あと{0}集めると出金できます</t>
   </si>
   <si>
     <t>MakeupUIForm.input</t>
   </si>
   <si>
+    <t>入力</t>
+  </si>
+  <si>
     <t>MakeupUIForm.record</t>
   </si>
   <si>
+    <t>履歴</t>
+  </si>
+  <si>
     <t>MakeupUIForm.title</t>
   </si>
   <si>
+    <t>出金</t>
+  </si>
+  <si>
     <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
+    <t>残高 {0}=$1</t>
+  </si>
+  <si>
     <t>PcardGiftUIForm.desc</t>
   </si>
   <si>
+    <t>広告を見ると、宝箱からゲームアイテムを獲得できます。</t>
+  </si>
+  <si>
     <t>QuitConfirmUIForm.desc</t>
   </si>
   <si>
+    <t>今やめるとライフを1つ失います。</t>
+  </si>
+  <si>
     <t>QuitConfirmUIForm.quitTxt</t>
   </si>
   <si>
+    <t>終了しますか？</t>
+  </si>
+  <si>
     <t>SettingPageUIForm.continue</t>
   </si>
   <si>
@@ -372,7 +377,13 @@
     <t>SettingPageUIForm.quit</t>
   </si>
   <si>
+    <t>終了</t>
+  </si>
+  <si>
     <t>TaskItem.infoTxt</t>
+  </si>
+  <si>
+    <t>{0}ステージをクリアしよう！</t>
   </si>
 </sst>
 </file>
@@ -408,9 +419,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +589,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
@@ -686,6478 +695,6 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -7172,12 +709,12 @@
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1092">
+            <xdr:cNvPr hidden="1" name="A1" id="1025">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
+                  <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7258,12 +795,12 @@
           <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1093">
+            <xdr:cNvPr hidden="1" name="A2" id="1026">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
+                  <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7344,12 +881,12 @@
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1094">
+            <xdr:cNvPr hidden="1" name="A3" id="1027">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
+                  <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7430,12 +967,12 @@
           <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1095">
+            <xdr:cNvPr hidden="1" name="A4" id="1028">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7516,12 +1053,12 @@
           <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1096">
+            <xdr:cNvPr hidden="1" name="A5" id="1029">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
+                  <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7602,12 +1139,12 @@
           <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1097">
+            <xdr:cNvPr hidden="1" name="A6" id="1030">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
+                  <a14:compatExt spid="_x0000_s1030"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7688,12 +1225,12 @@
           <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1098">
+            <xdr:cNvPr hidden="1" name="A7" id="1031">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
+                  <a14:compatExt spid="_x0000_s1031"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7774,12 +1311,12 @@
           <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1099">
+            <xdr:cNvPr hidden="1" name="A8" id="1032">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
+                  <a14:compatExt spid="_x0000_s1032"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7860,12 +1397,12 @@
           <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1100">
+            <xdr:cNvPr hidden="1" name="A9" id="1033">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
+                  <a14:compatExt spid="_x0000_s1033"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7946,12 +1483,12 @@
           <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1101">
+            <xdr:cNvPr hidden="1" name="A10" id="1034">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
+                  <a14:compatExt spid="_x0000_s1034"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8032,12 +1569,12 @@
           <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1102">
+            <xdr:cNvPr hidden="1" name="A11" id="1035">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
+                  <a14:compatExt spid="_x0000_s1035"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8118,12 +1655,12 @@
           <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1103">
+            <xdr:cNvPr hidden="1" name="A12" id="1036">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
+                  <a14:compatExt spid="_x0000_s1036"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8204,12 +1741,12 @@
           <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1104">
+            <xdr:cNvPr hidden="1" name="A13" id="1037">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
+                  <a14:compatExt spid="_x0000_s1037"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8290,12 +1827,12 @@
           <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1105">
+            <xdr:cNvPr hidden="1" name="A14" id="1038">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
+                  <a14:compatExt spid="_x0000_s1038"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8376,12 +1913,12 @@
           <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1106">
+            <xdr:cNvPr hidden="1" name="A15" id="1039">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
+                  <a14:compatExt spid="_x0000_s1039"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8462,12 +1999,12 @@
           <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1107">
+            <xdr:cNvPr hidden="1" name="A16" id="1040">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
+                  <a14:compatExt spid="_x0000_s1040"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8548,12 +2085,12 @@
           <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1108">
+            <xdr:cNvPr hidden="1" name="A17" id="1041">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
+                  <a14:compatExt spid="_x0000_s1041"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8634,12 +2171,12 @@
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1109">
+            <xdr:cNvPr hidden="1" name="A18" id="1042">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
+                  <a14:compatExt spid="_x0000_s1042"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8720,12 +2257,12 @@
           <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1110">
+            <xdr:cNvPr hidden="1" name="A19" id="1043">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
+                  <a14:compatExt spid="_x0000_s1043"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8806,12 +2343,12 @@
           <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1111">
+            <xdr:cNvPr hidden="1" name="A20" id="1044">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1111"/>
+                  <a14:compatExt spid="_x0000_s1044"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8892,12 +2429,12 @@
           <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1112">
+            <xdr:cNvPr hidden="1" name="A21" id="1045">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1112"/>
+                  <a14:compatExt spid="_x0000_s1045"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8978,12 +2515,12 @@
           <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1113">
+            <xdr:cNvPr hidden="1" name="A22" id="1046">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
+                  <a14:compatExt spid="_x0000_s1046"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9064,12 +2601,12 @@
           <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1114">
+            <xdr:cNvPr hidden="1" name="A23" id="1047">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
+                  <a14:compatExt spid="_x0000_s1047"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9150,12 +2687,12 @@
           <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1115">
+            <xdr:cNvPr hidden="1" name="A24" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
+                  <a14:compatExt spid="_x0000_s1048"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9236,12 +2773,12 @@
           <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1116">
+            <xdr:cNvPr hidden="1" name="A25" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
+                  <a14:compatExt spid="_x0000_s1049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9322,12 +2859,12 @@
           <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1117">
+            <xdr:cNvPr hidden="1" name="A26" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9408,12 +2945,12 @@
           <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1118">
+            <xdr:cNvPr hidden="1" name="A27" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
+                  <a14:compatExt spid="_x0000_s1051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9494,12 +3031,12 @@
           <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1119">
+            <xdr:cNvPr hidden="1" name="A28" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
+                  <a14:compatExt spid="_x0000_s1052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9580,12 +3117,12 @@
           <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1120">
+            <xdr:cNvPr hidden="1" name="A29" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
+                  <a14:compatExt spid="_x0000_s1053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9666,12 +3203,12 @@
           <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1121">
+            <xdr:cNvPr hidden="1" name="A30" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
+                  <a14:compatExt spid="_x0000_s1054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9752,12 +3289,12 @@
           <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1122">
+            <xdr:cNvPr hidden="1" name="A31" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1122"/>
+                  <a14:compatExt spid="_x0000_s1055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9838,12 +3375,12 @@
           <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1123">
+            <xdr:cNvPr hidden="1" name="A32" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1123"/>
+                  <a14:compatExt spid="_x0000_s1056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9924,12 +3461,12 @@
           <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1124">
+            <xdr:cNvPr hidden="1" name="A33" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1124"/>
+                  <a14:compatExt spid="_x0000_s1057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10010,12 +3547,12 @@
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1125">
+            <xdr:cNvPr hidden="1" name="A34" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1125"/>
+                  <a14:compatExt spid="_x0000_s1058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10096,12 +3633,12 @@
           <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1126">
+            <xdr:cNvPr hidden="1" name="A35" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1126"/>
+                  <a14:compatExt spid="_x0000_s1059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10182,12 +3719,12 @@
           <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1127">
+            <xdr:cNvPr hidden="1" name="A36" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1127"/>
+                  <a14:compatExt spid="_x0000_s1060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10268,12 +3805,12 @@
           <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1128">
+            <xdr:cNvPr hidden="1" name="A37" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1128"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10354,12 +3891,12 @@
           <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1129">
+            <xdr:cNvPr hidden="1" name="A38" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1129"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10440,12 +3977,12 @@
           <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1130">
+            <xdr:cNvPr hidden="1" name="A39" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1130"/>
+                  <a14:compatExt spid="_x0000_s1063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10526,12 +4063,12 @@
           <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1131">
+            <xdr:cNvPr hidden="1" name="A40" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1131"/>
+                  <a14:compatExt spid="_x0000_s1064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10612,12 +4149,12 @@
           <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1132">
+            <xdr:cNvPr hidden="1" name="A41" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1132"/>
+                  <a14:compatExt spid="_x0000_s1065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10698,12 +4235,12 @@
           <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1133">
+            <xdr:cNvPr hidden="1" name="A42" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1133"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10784,12 +4321,12 @@
           <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1134">
+            <xdr:cNvPr hidden="1" name="A43" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1134"/>
+                  <a14:compatExt spid="_x0000_s1067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10870,12 +4407,12 @@
           <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1135">
+            <xdr:cNvPr hidden="1" name="A44" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1135"/>
+                  <a14:compatExt spid="_x0000_s1068"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10956,12 +4493,12 @@
           <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1136">
+            <xdr:cNvPr hidden="1" name="A45" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1136"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11042,12 +4579,12 @@
           <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1137">
+            <xdr:cNvPr hidden="1" name="A46" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11128,12 +4665,12 @@
           <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1138">
+            <xdr:cNvPr hidden="1" name="A47" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11214,12 +4751,12 @@
           <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1139">
+            <xdr:cNvPr hidden="1" name="A48" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11300,12 +4837,12 @@
           <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1140">
+            <xdr:cNvPr hidden="1" name="A49" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11386,12 +4923,12 @@
           <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1141">
+            <xdr:cNvPr hidden="1" name="A50" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11472,12 +5009,12 @@
           <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1142">
+            <xdr:cNvPr hidden="1" name="A51" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11558,12 +5095,12 @@
           <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1143">
+            <xdr:cNvPr hidden="1" name="A52" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11644,12 +5181,12 @@
           <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1144">
+            <xdr:cNvPr hidden="1" name="A53" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11730,12 +5267,12 @@
           <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1145">
+            <xdr:cNvPr hidden="1" name="A54" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11816,12 +5353,12 @@
           <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1146">
+            <xdr:cNvPr hidden="1" name="A55" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11902,12 +5439,12 @@
           <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1147">
+            <xdr:cNvPr hidden="1" name="A56" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11988,12 +5525,12 @@
           <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1148">
+            <xdr:cNvPr hidden="1" name="A57" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12074,12 +5611,12 @@
           <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1149">
+            <xdr:cNvPr hidden="1" name="A58" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12160,12 +5697,12 @@
           <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1150">
+            <xdr:cNvPr hidden="1" name="A59" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12246,12 +5783,12 @@
           <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1151">
+            <xdr:cNvPr hidden="1" name="A60" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12332,12 +5869,12 @@
           <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1152">
+            <xdr:cNvPr hidden="1" name="A61" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12418,12 +5955,12 @@
           <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1153">
+            <xdr:cNvPr hidden="1" name="A62" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12504,12 +6041,12 @@
           <xdr:row>63</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1154">
+            <xdr:cNvPr hidden="1" name="A63" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12590,12 +6127,12 @@
           <xdr:row>64</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1155">
+            <xdr:cNvPr hidden="1" name="A64" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1155"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12676,12 +6213,12 @@
           <xdr:row>65</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1156">
+            <xdr:cNvPr hidden="1" name="A65" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1156"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12762,12 +6299,12 @@
           <xdr:row>66</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A66" id="1157">
+            <xdr:cNvPr hidden="1" name="A66" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1157"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12841,603 +6378,538 @@
   <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="34.0738721575056" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1" style="1"/>
+    <col min="2" max="2" width="45" customWidth="1" style="1"/>
+    <col min="3" max="3" width="60" customWidth="1" style="1"/>
+    <col min="4" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>1</v>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1"/>
-      <c r="B12" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>18</v>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1"/>
-      <c r="B13" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>23</v>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1"/>
-      <c r="B14" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>25</v>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>27</v>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>29</v>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>10</v>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>32</v>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1"/>
-      <c r="B19" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>34</v>
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>36</v>
+      <c r="B20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>38</v>
+      <c r="B21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>40</v>
+      <c r="B22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>42</v>
+      <c r="B23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>1</v>
+      <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>1</v>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>46</v>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>48</v>
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>50</v>
+      <c r="B28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>52</v>
+      <c r="B29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>54</v>
+      <c r="B30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>56</v>
+      <c r="B31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1"/>
-      <c r="B32" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>58</v>
+      <c r="B32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1"/>
-      <c r="B33" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>60</v>
+      <c r="B33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1"/>
-      <c r="B34" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>62</v>
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>64</v>
+      <c r="B35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1"/>
-      <c r="B36" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>1</v>
+      <c r="B36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1"/>
-      <c r="B37" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>1</v>
+      <c r="B37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1"/>
-      <c r="B38" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>1</v>
+      <c r="B38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1"/>
-      <c r="B39" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>69</v>
+      <c r="B39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1"/>
-      <c r="B40" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>71</v>
+      <c r="B40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1"/>
-      <c r="B41" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>73</v>
+      <c r="B41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1"/>
-      <c r="B42" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>75</v>
+      <c r="B42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1"/>
-      <c r="B43" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>77</v>
+      <c r="B43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1"/>
-      <c r="B44" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>79</v>
+      <c r="B44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>81</v>
+      <c r="B45" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>1</v>
+      <c r="B46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1"/>
-      <c r="B47" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>1</v>
+      <c r="B47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1"/>
-      <c r="B48" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>1</v>
+      <c r="B48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1"/>
-      <c r="B49" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>86</v>
+      <c r="B49" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1"/>
-      <c r="B50" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>1</v>
+      <c r="B50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1"/>
-      <c r="B51" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>1</v>
+      <c r="B51" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1"/>
-      <c r="B52" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>1</v>
+      <c r="B52" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1"/>
-      <c r="B53" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>1</v>
+      <c r="B53" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1"/>
-      <c r="B54" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>92</v>
+      <c r="B54" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1"/>
-      <c r="B55" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>94</v>
+      <c r="B55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1"/>
-      <c r="B56" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>1</v>
+      <c r="B56" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1"/>
-      <c r="B57" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>1</v>
+      <c r="B57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1"/>
-      <c r="B58" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>1</v>
+      <c r="B58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1"/>
-      <c r="B59" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>1</v>
+      <c r="B59" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1"/>
-      <c r="B60" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>1</v>
+      <c r="B60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1"/>
-      <c r="B61" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>1</v>
+      <c r="B61" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1"/>
-      <c r="B62" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>1</v>
+      <c r="B62" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1"/>
-      <c r="B63" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>1</v>
+      <c r="B63" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>1</v>
+      <c r="B64" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1"/>
-      <c r="B65" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>1</v>
+      <c r="B65" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1"/>
-      <c r="B66" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>1</v>
+      <c r="B66" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -13449,7 +6921,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1596" name="A1">
+            <control shapeId="1025" r:id="rId2" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13471,7 +6943,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1597" name="A2">
+            <control shapeId="1026" r:id="rId4" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13493,7 +6965,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1598" name="A3">
+            <control shapeId="1027" r:id="rId5" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13515,7 +6987,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1599" name="A4">
+            <control shapeId="1028" r:id="rId6" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13537,7 +7009,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1600" name="A5">
+            <control shapeId="1029" r:id="rId7" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13559,7 +7031,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1601" name="A6">
+            <control shapeId="1030" r:id="rId8" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13581,7 +7053,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1602" name="A7">
+            <control shapeId="1031" r:id="rId9" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13603,7 +7075,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1603" name="A8">
+            <control shapeId="1032" r:id="rId10" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13625,7 +7097,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1604" name="A9">
+            <control shapeId="1033" r:id="rId11" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13647,7 +7119,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1605" name="A10">
+            <control shapeId="1034" r:id="rId12" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13669,7 +7141,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1606" name="A11">
+            <control shapeId="1035" r:id="rId13" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13691,7 +7163,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1607" name="A12">
+            <control shapeId="1036" r:id="rId14" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13713,7 +7185,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1608" name="A13">
+            <control shapeId="1037" r:id="rId15" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13735,7 +7207,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1609" name="A14">
+            <control shapeId="1038" r:id="rId16" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13757,7 +7229,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1610" name="A15">
+            <control shapeId="1039" r:id="rId17" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13779,7 +7251,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1611" name="A16">
+            <control shapeId="1040" r:id="rId18" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13801,7 +7273,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1612" name="A17">
+            <control shapeId="1041" r:id="rId19" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13823,7 +7295,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1613" name="A18">
+            <control shapeId="1042" r:id="rId20" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13845,7 +7317,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1614" name="A19">
+            <control shapeId="1043" r:id="rId21" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13867,7 +7339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1615" name="A20">
+            <control shapeId="1044" r:id="rId22" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13889,7 +7361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1616" name="A21">
+            <control shapeId="1045" r:id="rId23" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13911,7 +7383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1617" name="A22">
+            <control shapeId="1046" r:id="rId24" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13933,7 +7405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1618" name="A23">
+            <control shapeId="1047" r:id="rId25" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13955,7 +7427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1619" name="A24">
+            <control shapeId="1048" r:id="rId26" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13977,7 +7449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1620" name="A25">
+            <control shapeId="1049" r:id="rId27" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13999,7 +7471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1621" name="A26">
+            <control shapeId="1050" r:id="rId28" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14021,7 +7493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1622" name="A27">
+            <control shapeId="1051" r:id="rId29" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14043,7 +7515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1623" name="A28">
+            <control shapeId="1052" r:id="rId30" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14065,7 +7537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1624" name="A29">
+            <control shapeId="1053" r:id="rId31" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14087,7 +7559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1625" name="A30">
+            <control shapeId="1054" r:id="rId32" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14109,7 +7581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId1626" name="A31">
+            <control shapeId="1055" r:id="rId33" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14131,7 +7603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId1627" name="A32">
+            <control shapeId="1056" r:id="rId34" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14153,7 +7625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId1628" name="A33">
+            <control shapeId="1057" r:id="rId35" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14175,7 +7647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId1629" name="A34">
+            <control shapeId="1058" r:id="rId36" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14197,7 +7669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId1630" name="A35">
+            <control shapeId="1059" r:id="rId37" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14219,7 +7691,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId1631" name="A36">
+            <control shapeId="1060" r:id="rId38" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14241,7 +7713,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId1632" name="A37">
+            <control shapeId="1061" r:id="rId39" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14263,7 +7735,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId1633" name="A38">
+            <control shapeId="1062" r:id="rId40" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14285,7 +7757,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId1634" name="A39">
+            <control shapeId="1063" r:id="rId41" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14307,7 +7779,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId1635" name="A40">
+            <control shapeId="1064" r:id="rId42" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14329,7 +7801,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId1636" name="A41">
+            <control shapeId="1065" r:id="rId43" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14351,7 +7823,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId1637" name="A42">
+            <control shapeId="1066" r:id="rId44" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14373,7 +7845,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId1638" name="A43">
+            <control shapeId="1067" r:id="rId45" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14395,7 +7867,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId1639" name="A44">
+            <control shapeId="1068" r:id="rId46" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14417,7 +7889,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId1640" name="A45">
+            <control shapeId="1069" r:id="rId47" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14439,7 +7911,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId1641" name="A46">
+            <control shapeId="1070" r:id="rId48" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14461,7 +7933,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId1642" name="A47">
+            <control shapeId="1071" r:id="rId49" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14483,7 +7955,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId1643" name="A48">
+            <control shapeId="1072" r:id="rId50" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14505,7 +7977,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId1644" name="A49">
+            <control shapeId="1073" r:id="rId51" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14527,7 +7999,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId1645" name="A50">
+            <control shapeId="1074" r:id="rId52" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14549,7 +8021,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId1646" name="A51">
+            <control shapeId="1075" r:id="rId53" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14571,7 +8043,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId1647" name="A52">
+            <control shapeId="1076" r:id="rId54" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14593,7 +8065,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId1648" name="A53">
+            <control shapeId="1077" r:id="rId55" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14615,7 +8087,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId1649" name="A54">
+            <control shapeId="1078" r:id="rId56" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14637,7 +8109,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId1650" name="A55">
+            <control shapeId="1079" r:id="rId57" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14659,7 +8131,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId1651" name="A56">
+            <control shapeId="1080" r:id="rId58" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14681,7 +8153,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId1652" name="A57">
+            <control shapeId="1081" r:id="rId59" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14703,7 +8175,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId1653" name="A58">
+            <control shapeId="1082" r:id="rId60" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14725,7 +8197,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId1654" name="A59">
+            <control shapeId="1083" r:id="rId61" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14747,7 +8219,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId1655" name="A60">
+            <control shapeId="1084" r:id="rId62" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14769,7 +8241,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId1656" name="A61">
+            <control shapeId="1085" r:id="rId63" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14791,7 +8263,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId1657" name="A62">
+            <control shapeId="1086" r:id="rId64" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14813,7 +8285,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId1658" name="A63">
+            <control shapeId="1087" r:id="rId65" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14835,7 +8307,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1155" r:id="rId1659" name="A64">
+            <control shapeId="1088" r:id="rId66" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14857,7 +8329,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1156" r:id="rId1660" name="A65">
+            <control shapeId="1089" r:id="rId67" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14879,7 +8351,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1157" r:id="rId1661" name="A66">
+            <control shapeId="1090" r:id="rId68" name="A66">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -140,7 +140,7 @@
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
-    <t>交換</t>
+    <t>出金</t>
   </si>
   <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
@@ -341,9 +341,6 @@
     <t>MakeupUIForm.title</t>
   </si>
   <si>
-    <t>出金</t>
-  </si>
-  <si>
     <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
@@ -384,6 +381,9 @@
   </si>
   <si>
     <t>{0}ステージをクリアしよう！</t>
+  </si>
+  <si>
+    <t>MakeupRecordUIForm.title</t>
   </si>
 </sst>
 </file>
@@ -680,6 +680,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6370,12 +6374,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A67" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6845,44 +6935,44 @@
         <v>108</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -6890,7 +6980,7 @@
     </row>
     <row r="64">
       <c r="B64" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>11</v>
@@ -6898,18 +6988,26 @@
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C66" s="1" t="s">
+    </row>
+    <row r="67">
+      <c r="B67" s="1" t="s">
         <v>123</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -8371,6 +8469,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1091" r:id="rId69" name="A67">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -278,6 +278,9 @@
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
+    <t>完了</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
@@ -384,6 +387,66 @@
   </si>
   <si>
     <t>MakeupRecordUIForm.title</t>
+  </si>
+  <si>
+    <t>AddLifeUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>追加ライフ</t>
+  </si>
+  <si>
+    <t>AddPropUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>ロケット</t>
+  </si>
+  <si>
+    <t>PlayLoadingUIForm.loading</t>
+  </si>
+  <si>
+    <t>読み込み中...</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quit</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.avatarTxt</t>
+  </si>
+  <si>
+    <t>アバターを選択：</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterDesc</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterAgainDesc</t>
+  </si>
+  <si>
+    <t>PayPalアカウントを再入力</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.confirm</t>
+  </si>
+  <si>
+    <t>確認</t>
+  </si>
+  <si>
+    <t>TaskItem.adTxt</t>
+  </si>
+  <si>
+    <t>広告を見よう！</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>無料</t>
+  </si>
+  <si>
+    <t>TaskItem.go</t>
+  </si>
+  <si>
+    <t>進む</t>
   </si>
 </sst>
 </file>
@@ -684,7 +747,51 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6460,12 +6567,958 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A68" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A70" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A71" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A72" id="1096">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1096"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A73" id="1097">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1097"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A74" id="1098">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1098"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A75" id="1099">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1099"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A76" id="1100">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1100"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A77" id="1101">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1101"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A78" id="1102">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1102"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6847,92 +7900,92 @@
         <v>87</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>42</v>
@@ -6940,39 +7993,39 @@
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -6980,7 +8033,7 @@
     </row>
     <row r="64">
       <c r="B64" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>11</v>
@@ -6988,26 +8041,114 @@
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -8491,6 +9632,248 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1092" r:id="rId70" name="A68">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId72" name="A70">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId73" name="A71">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1096" r:id="rId74" name="A72">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1097" r:id="rId75" name="A73">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1098" r:id="rId76" name="A74">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1099" r:id="rId77" name="A75">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1100" r:id="rId78" name="A76">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1101" r:id="rId79" name="A77">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1102" r:id="rId80" name="A78">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -447,6 +447,15 @@
   </si>
   <si>
     <t>進む</t>
+  </si>
+  <si>
+    <t>cashoutHint</t>
+  </si>
+  <si>
+    <t>{0}ステージをクリアし、残高が{1}に達すると受け取れます。</t>
+  </si>
+  <si>
+    <t>MakeupItem.cashout</t>
   </si>
 </sst>
 </file>
@@ -795,7 +804,15 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -7513,12 +7530,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A79" id="1103">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1103"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A80" id="1104">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1104"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8149,6 +8338,22 @@
       </c>
       <c r="C78" s="1" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -9874,6 +10079,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1103" r:id="rId81" name="A79">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1104" r:id="rId82" name="A80">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -188,7 +188,7 @@
     <t>GuidTxt1</t>
   </si>
   <si>
-    <t>タップして移動</t>
+    <t>そのアイテムをタップして大砲を撃とう！</t>
   </si>
   <si>
     <t>GuidTxt3</t>
@@ -456,6 +456,42 @@
   </si>
   <si>
     <t>MakeupItem.cashout</t>
+  </si>
+  <si>
+    <t>GuidTxt2</t>
+  </si>
+  <si>
+    <t>弾がなくなる前にすべてのアイテムを消そう！</t>
+  </si>
+  <si>
+    <t>MakeupRecordItem.bouns</t>
+  </si>
+  <si>
+    <t>本日の賞金総額</t>
+  </si>
+  <si>
+    <t>PlayUIForm.txtHint</t>
+  </si>
+  <si>
+    <t>テーブルの上のアイテムをタップ</t>
+  </si>
+  <si>
+    <t>MakeupItem.reach</t>
+  </si>
+  <si>
+    <t>必要残高</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm.desc</t>
+  </si>
+  <si>
+    <t>ブースターを選択：</t>
+  </si>
+  <si>
+    <t>MakeupPaymentEndUIForm.desc</t>
+  </si>
+  <si>
+    <t>温かいご寄付をありがとうございます！</t>
   </si>
 </sst>
 </file>
@@ -601,19 +637,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -816,6 +852,30 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7702,12 +7762,528 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A81" id="1105">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1105"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A82" id="1106">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1106"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A83" id="1107">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1107"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A84" id="1108">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1108"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A85" id="1109">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1109"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>86</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A86" id="1110">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1110"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8354,6 +8930,54 @@
       </c>
       <c r="C80" s="1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -10123,6 +10747,138 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1105" r:id="rId83" name="A81">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1106" r:id="rId84" name="A82">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1107" r:id="rId85" name="A83">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1108" r:id="rId86" name="A84">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1109" r:id="rId87" name="A85">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1110" r:id="rId88" name="A86">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>86</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -26,24 +26,6 @@
     <t>続けますか？</t>
   </si>
   <si>
-    <t>ArrowMazeOverUIForm.GameOver</t>
-  </si>
-  <si>
-    <t>連勝チャレンジ失敗</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.restart</t>
-  </si>
-  <si>
-    <t>やり直す</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.Revive</t>
-  </si>
-  <si>
-    <t>復活</t>
-  </si>
-  <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
   </si>
   <si>
@@ -56,319 +38,241 @@
     <t>受け取る</t>
   </si>
   <si>
-    <t>ArrowRewardDialogUIForm.Continue</t>
+    <t>ArrowRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>おめでとう！</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.OFF</t>
+  </si>
+  <si>
+    <t>オフ</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.ON</t>
+  </si>
+  <si>
+    <t>オン</t>
+  </si>
+  <si>
+    <t>ArrowUITopbar.cashOut</t>
+  </si>
+  <si>
+    <t>出金</t>
+  </si>
+  <si>
+    <t>ArrowWithdrawalInfoItem.infoTxt</t>
+  </si>
+  <si>
+    <t>プレイヤー{0}さん、({1})のクリアと{2}の獲得、おめでとうございます！</t>
+  </si>
+  <si>
+    <t>claim</t>
+  </si>
+  <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Enteraccountnumber</t>
+  </si>
+  <si>
+    <t>口座を入力</t>
+  </si>
+  <si>
+    <t>EnterCPF</t>
+  </si>
+  <si>
+    <t>CPFを入力</t>
+  </si>
+  <si>
+    <t>Enteremail</t>
+  </si>
+  <si>
+    <t>メールアドレスを確認</t>
+  </si>
+  <si>
+    <t>EnterFullName</t>
+  </si>
+  <si>
+    <t>氏名を入力</t>
+  </si>
+  <si>
+    <t>EnterPayPalaccount</t>
+  </si>
+  <si>
+    <t>PayPalアカウントを入力</t>
+  </si>
+  <si>
+    <t>GuidTxt1</t>
+  </si>
+  <si>
+    <t>そのアイテムをタップして大砲を撃とう！</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>ホーム</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>設定</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
+    <t>タスク</t>
+  </si>
+  <si>
+    <t>InfoErrTips1</t>
+  </si>
+  <si>
+    <t>有効なメールアドレスを入力してください</t>
+  </si>
+  <si>
+    <t>InfoErrTips2</t>
+  </si>
+  <si>
+    <t>有効なCPFを入力してください</t>
+  </si>
+  <si>
+    <t>InfoErrTips3</t>
+  </si>
+  <si>
+    <t>PayPalアカウントには有効なメールアドレスが必要です</t>
+  </si>
+  <si>
+    <t>InfoErrTips4</t>
+  </si>
+  <si>
+    <t>氏名を入力してください</t>
+  </si>
+  <si>
+    <t>InfoErrTips5</t>
+  </si>
+  <si>
+    <t>口座番号を入力してください</t>
+  </si>
+  <si>
+    <t>InfoErrTips6</t>
+  </si>
+  <si>
+    <t>お支払い方法を選択してください</t>
+  </si>
+  <si>
+    <t>InfoErrTips7</t>
+  </si>
+  <si>
+    <t>お支払い情報を保存しました</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>ステージ{0}</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.next</t>
+  </si>
+  <si>
+    <t>次へ</t>
+  </si>
+  <si>
+    <t>MakeUpFail</t>
+  </si>
+  <si>
+    <t>申し訳ありません。交換に失敗しました。</t>
+  </si>
+  <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t>2回入力したPayPalアカウントが一致していることを確認してください。</t>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
+    <t>正しい形式でメールアドレスを入力してください。</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>出金処理中</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>お支払い方法</t>
+  </si>
+  <si>
+    <t>MakeUpStep1</t>
+  </si>
+  <si>
+    <t>ステージ{0}をクリアすると出金できます</t>
+  </si>
+  <si>
+    <t>MakeUpStep2</t>
+  </si>
+  <si>
+    <t>あと{0}集めると出金できます</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
+    <t>履歴</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.title</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
+    <t>残高 {0}=$1</t>
+  </si>
+  <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
+    <t>広告を見ると、宝箱からゲームアイテムを獲得できます。</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>今やめるとライフを1つ失います。</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>終了しますか？</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>続ける</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.NextLevel</t>
-  </si>
-  <si>
-    <t>次のステージ</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>コンボ報酬</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.winTitle</t>
-  </si>
-  <si>
-    <t>ステージクリア</t>
-  </si>
-  <si>
-    <t>ArrowRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>おめでとう！</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.OFF</t>
-  </si>
-  <si>
-    <t>オフ</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.ON</t>
-  </si>
-  <si>
-    <t>オン</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Home</t>
-  </si>
-  <si>
-    <t>ホーム</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Music</t>
-  </si>
-  <si>
-    <t>音楽</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Privacy</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Resume</t>
-  </si>
-  <si>
-    <t>再開</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Sound</t>
-  </si>
-  <si>
-    <t>サウンド</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Text_Title</t>
-  </si>
-  <si>
-    <t>設定</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Vibrate</t>
-  </si>
-  <si>
-    <t>振動</t>
-  </si>
-  <si>
-    <t>ArrowUITopbar.cashOut</t>
-  </si>
-  <si>
-    <t>出金</t>
-  </si>
-  <si>
-    <t>ArrowWithdrawalInfoItem.infoTxt</t>
-  </si>
-  <si>
-    <t>プレイヤー{0}さん、({1})のクリアと{2}の獲得、おめでとうございます！</t>
-  </si>
-  <si>
-    <t>claim</t>
-  </si>
-  <si>
-    <t>CoinRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Enteraccountnumber</t>
-  </si>
-  <si>
-    <t>口座を入力</t>
-  </si>
-  <si>
-    <t>EnterCPF</t>
-  </si>
-  <si>
-    <t>CPFを入力</t>
-  </si>
-  <si>
-    <t>Enteremail</t>
-  </si>
-  <si>
-    <t>メールアドレスを確認</t>
-  </si>
-  <si>
-    <t>EnterFullName</t>
-  </si>
-  <si>
-    <t>氏名を入力</t>
-  </si>
-  <si>
-    <t>EnterPayPalaccount</t>
-  </si>
-  <si>
-    <t>PayPalアカウントを入力</t>
-  </si>
-  <si>
-    <t>GuidTxt1</t>
-  </si>
-  <si>
-    <t>そのアイテムをタップして大砲を撃とう！</t>
-  </si>
-  <si>
-    <t>GuidTxt3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ここをタップして出金 </t>
-  </si>
-  <si>
-    <t>GuidTxt4</t>
-  </si>
-  <si>
-    <t>指を広げて拡大</t>
-  </si>
-  <si>
-    <t>GuidTxt5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在の残高はこちらで確認できます。 </t>
-  </si>
-  <si>
-    <t>GuidTxt6</t>
-  </si>
-  <si>
-    <t>条件を達成すると出金できます。</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.home</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.setting</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.task</t>
-  </si>
-  <si>
-    <t>タスク</t>
-  </si>
-  <si>
-    <t>InfoErrTips1</t>
-  </si>
-  <si>
-    <t>有効なメールアドレスを入力してください</t>
-  </si>
-  <si>
-    <t>InfoErrTips2</t>
-  </si>
-  <si>
-    <t>有効なCPFを入力してください</t>
-  </si>
-  <si>
-    <t>InfoErrTips3</t>
-  </si>
-  <si>
-    <t>PayPalアカウントには有効なメールアドレスが必要です</t>
-  </si>
-  <si>
-    <t>InfoErrTips4</t>
-  </si>
-  <si>
-    <t>氏名を入力してください</t>
-  </si>
-  <si>
-    <t>InfoErrTips5</t>
-  </si>
-  <si>
-    <t>口座番号を入力してください</t>
-  </si>
-  <si>
-    <t>InfoErrTips6</t>
-  </si>
-  <si>
-    <t>お支払い方法を選択してください</t>
-  </si>
-  <si>
-    <t>InfoErrTips7</t>
-  </si>
-  <si>
-    <t>お支払い情報を保存しました</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>ステージ{0}</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.complete</t>
-  </si>
-  <si>
-    <t>完了</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.next</t>
-  </si>
-  <si>
-    <t>次へ</t>
-  </si>
-  <si>
-    <t>MakeUpFail</t>
-  </si>
-  <si>
-    <t>申し訳ありません。交換に失敗しました。</t>
-  </si>
-  <si>
-    <t>makeupInfoHint1</t>
-  </si>
-  <si>
-    <t>2回入力したPayPalアカウントが一致していることを確認してください。</t>
-  </si>
-  <si>
-    <t>makeupInfoHint2</t>
-  </si>
-  <si>
-    <t>正しい形式でメールアドレスを入力してください。</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>出金処理中</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>お支払い方法</t>
-  </si>
-  <si>
-    <t>MakeUpStep1</t>
-  </si>
-  <si>
-    <t>ステージ{0}をクリアすると出金できます</t>
-  </si>
-  <si>
-    <t>MakeUpStep2</t>
-  </si>
-  <si>
-    <t>あと{0}集めると出金できます</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.input</t>
-  </si>
-  <si>
-    <t>入力</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.record</t>
-  </si>
-  <si>
-    <t>履歴</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.title</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.txtBalance</t>
-  </si>
-  <si>
-    <t>残高 {0}=$1</t>
-  </si>
-  <si>
-    <t>PcardGiftUIForm.desc</t>
-  </si>
-  <si>
-    <t>広告を見ると、宝箱からゲームアイテムを獲得できます。</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.desc</t>
-  </si>
-  <si>
-    <t>今やめるとライフを1つ失います。</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.quitTxt</t>
-  </si>
-  <si>
-    <t>終了しますか？</t>
-  </si>
-  <si>
-    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>SettingPageUIForm.privacy</t>
@@ -549,27 +453,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -589,23 +493,23 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
@@ -621,7 +525,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,7 +533,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
@@ -637,11 +541,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -653,11 +557,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -665,7 +569,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -673,31 +577,31 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
@@ -709,7 +613,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -717,11 +621,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
@@ -733,11 +637,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
@@ -765,7 +669,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,7 +677,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
@@ -796,83 +700,11 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6730,1560 +6562,12 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1093">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1094">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A71" id="1095">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A72" id="1096">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A73" id="1097">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A74" id="1098">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A75" id="1099">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A76" id="1100">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A77" id="1101">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A78" id="1102">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A79" id="1103">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A80" id="1104">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A81" id="1105">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A82" id="1106">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A83" id="1107">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A84" id="1108">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A85" id="1109">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>86</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A86" id="1110">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8369,119 +6653,119 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -8489,199 +6773,199 @@
         <v>46</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
@@ -8713,95 +6997,95 @@
         <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -8825,159 +7109,15 @@
         <v>124</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -10483,402 +8623,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId71" name="A69">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId72" name="A70">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId73" name="A71">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId74" name="A72">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId75" name="A73">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId76" name="A74">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId77" name="A75">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId78" name="A76">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId79" name="A77">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId80" name="A78">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId81" name="A79">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId82" name="A80">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId83" name="A81">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId84" name="A82">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId85" name="A83">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId86" name="A84">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId87" name="A85">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId88" name="A86">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>86</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -396,6 +396,12 @@
   </si>
   <si>
     <t>温かいご寄付をありがとうございます！</t>
+  </si>
+  <si>
+    <t>giftHint</t>
+  </si>
+  <si>
+    <t>宝箱を集めよう</t>
   </si>
 </sst>
 </file>
@@ -700,6 +706,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6562,12 +6572,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -7118,6 +7214,14 @@
       </c>
       <c r="C68" s="1" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -8623,6 +8727,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>
